--- a/JPD/documents/full_jpd.xlsx
+++ b/JPD/documents/full_jpd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\JPD\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74619E3E-B3E8-4B04-AC9E-52780AB77C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2AE732-036A-4190-B3BC-7782359E3A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{FA3ADD2E-6701-4EA2-BF3C-245AE1375C42}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t>イベント</t>
   </si>
@@ -498,10 +498,100 @@
     <t>～ねん</t>
   </si>
   <si>
-    <t>～</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 3  楽しい週末</t>
+  </si>
+  <si>
+    <t>～回</t>
+  </si>
+  <si>
+    <t>～かい</t>
+  </si>
+  <si>
+    <t>～冊</t>
+  </si>
+  <si>
+    <t>～さつ</t>
+  </si>
+  <si>
+    <t>～杯</t>
+  </si>
+  <si>
+    <t>～はい</t>
+  </si>
+  <si>
+    <t>～本</t>
+  </si>
+  <si>
+    <t>～ほん</t>
+  </si>
+  <si>
+    <t>～料理</t>
+  </si>
+  <si>
+    <t>～りょうり</t>
+  </si>
+  <si>
+    <t>イタリア料理</t>
+  </si>
+  <si>
+    <t>およぎます</t>
+  </si>
+  <si>
+    <t>泳ぎます　「泳ぐ」</t>
+  </si>
+  <si>
+    <t>描きます　「書く」</t>
+  </si>
+  <si>
+    <t>かきます</t>
+  </si>
+  <si>
+    <t>集めます　「集める」</t>
+  </si>
+  <si>
+    <t>あつめます</t>
+  </si>
+  <si>
+    <t>運転します　「運転する」</t>
+  </si>
+  <si>
+    <t>うんてんします</t>
+  </si>
+  <si>
+    <t>特に</t>
+  </si>
+  <si>
+    <t>とくに</t>
+  </si>
+  <si>
+    <t>いつも</t>
+  </si>
+  <si>
+    <t>よく</t>
+  </si>
+  <si>
+    <t>私はよく映画を見ます。</t>
+  </si>
+  <si>
+    <t>ときどき</t>
+  </si>
+  <si>
+    <t>あまり</t>
+  </si>
+  <si>
+    <t>あまりテレビをみません。</t>
+  </si>
+  <si>
+    <t>全然</t>
+  </si>
+  <si>
+    <t>ぜんぜん</t>
+  </si>
+  <si>
+    <t>でも</t>
+  </si>
+  <si>
+    <t>だけ</t>
   </si>
 </sst>
 </file>
@@ -616,9 +706,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -628,9 +718,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1068,12 +1158,12 @@
       <c r="A1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
@@ -1083,7 +1173,7 @@
         <v>90</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1097,7 +1187,7 @@
       <c r="C4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1111,7 +1201,7 @@
       <c r="C5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="4" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1123,7 +1213,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1135,7 +1225,7 @@
         <v>96</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="4" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1149,7 +1239,7 @@
       <c r="C8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="4" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1163,7 +1253,7 @@
       <c r="C9" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="4" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1177,7 +1267,7 @@
       <c r="C10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="4" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1189,7 +1279,7 @@
         <v>103</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="4" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1201,7 +1291,7 @@
         <v>104</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="4" t="s">
         <v>116</v>
       </c>
     </row>
@@ -1215,7 +1305,7 @@
       <c r="C13" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="4" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1229,7 +1319,7 @@
       <c r="C14" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="4" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1243,7 +1333,7 @@
       <c r="C15" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="4" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1257,7 +1347,7 @@
       <c r="C16" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="4" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1271,7 +1361,7 @@
       <c r="C17" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="4" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1280,10 +1370,12 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1291,9 +1383,13 @@
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="8" t="s">
+      <c r="B19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1301,9 +1397,13 @@
       <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="8" t="s">
+      <c r="B20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>124</v>
       </c>
     </row>
@@ -1311,9 +1411,13 @@
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="8" t="s">
+      <c r="B21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1321,17 +1425,23 @@
       <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="8" t="s">
+      <c r="B22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>161</v>
+      </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="4" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1339,9 +1449,13 @@
       <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="8" t="s">
+      <c r="B24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1349,9 +1463,13 @@
       <c r="A25" s="2">
         <v>22</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="8" t="s">
+      <c r="B25" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1359,9 +1477,13 @@
       <c r="A26" s="2">
         <v>23</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="8" t="s">
+      <c r="B26" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1369,9 +1491,13 @@
       <c r="A27" s="2">
         <v>24</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="8" t="s">
+      <c r="B27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1379,9 +1505,13 @@
       <c r="A28" s="2">
         <v>25</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="8" t="s">
+      <c r="B28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1389,9 +1519,11 @@
       <c r="A29" s="2">
         <v>26</v>
       </c>
-      <c r="B29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="5" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1399,17 +1531,21 @@
       <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="5" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="5" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1417,27 +1553,33 @@
       <c r="A32" s="2">
         <v>28</v>
       </c>
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>175</v>
+      </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="5" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="A33" s="2">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>29</v>
-      </c>
-      <c r="B34" s="2"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="5" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1445,19 +1587,25 @@
       <c r="A35" s="2">
         <v>30</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="9" t="s">
+      <c r="B35" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
+      <c r="A36" s="3">
         <v>31</v>
       </c>
-      <c r="B36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="5" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1465,19 +1613,21 @@
       <c r="A37" s="2">
         <v>32</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
@@ -1487,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1499,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1513,7 +1663,7 @@
       <c r="C43" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1525,7 +1675,7 @@
         <v>4</v>
       </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1537,7 +1687,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="4" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1549,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="4" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1559,7 +1709,7 @@
         <v>7</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1573,7 +1723,7 @@
       <c r="C48" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1583,7 +1733,7 @@
         <v>35</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1597,7 +1747,7 @@
       <c r="C50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1611,7 +1761,7 @@
       <c r="C51" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1625,7 +1775,7 @@
       <c r="C52" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1635,7 +1785,7 @@
         <v>16</v>
       </c>
       <c r="C53" s="2"/>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1649,7 +1799,7 @@
       <c r="C54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="4" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1661,7 +1811,7 @@
         <v>19</v>
       </c>
       <c r="C55" s="2"/>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1671,7 +1821,7 @@
         <v>20</v>
       </c>
       <c r="C56" s="2"/>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="4" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1685,7 +1835,7 @@
       <c r="C57" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="4" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1697,7 +1847,7 @@
         <v>23</v>
       </c>
       <c r="C58" s="2"/>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1709,7 +1859,7 @@
         <v>24</v>
       </c>
       <c r="C59" s="2"/>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1723,17 +1873,17 @@
       <c r="C60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
+      <c r="A63" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
@@ -1745,7 +1895,7 @@
       <c r="C64" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="4" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1757,7 +1907,7 @@
         <v>50</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="4" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1769,7 +1919,7 @@
       <c r="C66" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="4" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1783,7 +1933,7 @@
       <c r="C67" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1797,7 +1947,7 @@
       <c r="C68" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="4" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1811,7 +1961,7 @@
       <c r="C69" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="4" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1825,7 +1975,7 @@
       <c r="C70" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1839,7 +1989,7 @@
       <c r="C71" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="4" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1853,7 +2003,7 @@
       <c r="C72" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1867,7 +2017,7 @@
       <c r="C73" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="4" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1881,7 +2031,7 @@
       <c r="C74" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="4" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1895,7 +2045,7 @@
       <c r="C75" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="4" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1909,7 +2059,7 @@
       <c r="C76" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D76" s="4" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1921,7 +2071,7 @@
         <v>88</v>
       </c>
       <c r="C77" s="2"/>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="4" t="s">
         <v>73</v>
       </c>
     </row>

--- a/JPD/documents/full_jpd.xlsx
+++ b/JPD/documents/full_jpd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\JPD\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2AE732-036A-4190-B3BC-7782359E3A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6B7598-3B9D-490D-AD7F-9498D3B5CBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{FA3ADD2E-6701-4EA2-BF3C-245AE1375C42}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="278">
   <si>
     <t>イベント</t>
   </si>
@@ -592,13 +592,347 @@
   </si>
   <si>
     <t>だけ</t>
+  </si>
+  <si>
+    <t>例：</t>
+  </si>
+  <si>
+    <t>あさ、ジョギングをして、シャクーをあびて、かいしゃへ行きます。</t>
+  </si>
+  <si>
+    <t>Ｖて、それから。。。Ｖました。</t>
+  </si>
+  <si>
+    <t>Ｖ１て、Ｖ２て、。。。Ｖます/ました。</t>
+  </si>
+  <si>
+    <t>昨日、６じにおきて、ジョギングをして、それからあさごはんを食べました。</t>
+  </si>
+  <si>
+    <t>どうやってＶますか。</t>
+  </si>
+  <si>
+    <t>LIÊN KẾT ĐỘNG TỪ「どうし」</t>
+  </si>
+  <si>
+    <t>LIỆT KÊ HÀNH ĐỘNG</t>
+  </si>
+  <si>
+    <t>→ LÀM CÁCH NÀO ĐỂ LÀM「 V1」?</t>
+  </si>
+  <si>
+    <t>→Ｖ１て、Ｖ２て、。。。Ｖます。</t>
+  </si>
+  <si>
+    <t>→ TÔI ĐÃ LÀM 「V1」RỒI LÀM「 V2」。。。LÀM「 V」</t>
+  </si>
+  <si>
+    <t>ーどうやってきっぷを買いますか。</t>
+  </si>
+  <si>
+    <t>Làm cách nào để mua vé ạ?</t>
+  </si>
+  <si>
+    <t>Xin hãy cho tiền vào đây, rồi ấn cái nút này.</t>
+  </si>
+  <si>
+    <t>ーここにおかねをいれて、このボタンをおしてください。</t>
+  </si>
+  <si>
+    <t>漢字</t>
+  </si>
+  <si>
+    <t>好 HẢO</t>
+  </si>
+  <si>
+    <t>外国　「がいこく」　nước ngoài</t>
+  </si>
+  <si>
+    <t>外国語　「がいこくご」　ngoại ngữ</t>
+  </si>
+  <si>
+    <t>文法</t>
+  </si>
+  <si>
+    <t>好き(な)　「すきな」　thích</t>
+  </si>
+  <si>
+    <t>大好き　「だいすき」　rất thích</t>
+  </si>
+  <si>
+    <t>大好物　「だいこうぶつ」　món yêu thích</t>
+  </si>
+  <si>
+    <t>歌 CA</t>
+  </si>
+  <si>
+    <t>歌　「うた」bài hát</t>
+  </si>
+  <si>
+    <t>歌う　「うたう」　hát</t>
+  </si>
+  <si>
+    <t>国歌　「こっか」　Quốc ca</t>
+  </si>
+  <si>
+    <t>短歌　「たんか」　thơ ngắn</t>
+  </si>
+  <si>
+    <t>音 ÂM</t>
+  </si>
+  <si>
+    <t>音　「おと」　âm thanh</t>
+  </si>
+  <si>
+    <t>音読み　「お   んよみ」　âm On</t>
+  </si>
+  <si>
+    <t>楽 NHẠC, LẠC</t>
+  </si>
+  <si>
+    <t>楽しい　「たのしい」　vui vẻ</t>
+  </si>
+  <si>
+    <t>音楽　「おんがく」　âm nhạc</t>
+  </si>
+  <si>
+    <t>車 XA</t>
+  </si>
+  <si>
+    <t>車　「くるま」　xe hơi</t>
+  </si>
+  <si>
+    <t>映 ẢNH, ÁNH</t>
+  </si>
+  <si>
+    <t>映画　「えいが」　phim</t>
+  </si>
+  <si>
+    <t>画 HỌA, HOẠCH</t>
+  </si>
+  <si>
+    <t>計画　「けいかく」　　kế hoạch, dự án</t>
+  </si>
+  <si>
+    <t>旅 LỮ</t>
+  </si>
+  <si>
+    <t>旅　「たび」　chuyến đi, du lịch, cuộc hành trình</t>
+  </si>
+  <si>
+    <t>旅行　「りょこう」　du lịch</t>
+  </si>
+  <si>
+    <t>海 HẢI</t>
+  </si>
+  <si>
+    <t>海　「うみ」　biển</t>
+  </si>
+  <si>
+    <t>海水　「かいすい」　nước biển</t>
+  </si>
+  <si>
+    <t>外 NGOẠI, NGOÀI</t>
+  </si>
+  <si>
+    <t>家の外　「いえのそと」　bên ngoài nhà</t>
+  </si>
+  <si>
+    <t>外国人　「がいこくじん」　người nước ngoài</t>
+  </si>
+  <si>
+    <t>社外　「しゃがい」　ngoài công ty, bên ngoài doanh nghiệp</t>
+  </si>
+  <si>
+    <t>海外　「かいがい」　hải ngoại, ngước ngoài</t>
+  </si>
+  <si>
+    <t>辞書形　「Ｖる」：Thể nguyên dạng (từ điển) của động từ</t>
+  </si>
+  <si>
+    <t>「じしょけ」 là dạng ngắn của 「Ｖます」</t>
+  </si>
+  <si>
+    <t>Ｖます　→　Ｖる</t>
+  </si>
+  <si>
+    <t>Động từ nhóm 3 「三グループ」</t>
+  </si>
+  <si>
+    <t>Động từ nhóm 2 「ニグループ」</t>
+  </si>
+  <si>
+    <t>Động từ nhóm 1 「一グループ」</t>
+  </si>
+  <si>
+    <t>来ます→くる</t>
+  </si>
+  <si>
+    <t>します→する</t>
+  </si>
+  <si>
+    <t>食べます→食べる</t>
+  </si>
+  <si>
+    <t>見ます→見る</t>
+  </si>
+  <si>
+    <r>
+      <t>Ｖ</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Mincho"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ます</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Mincho"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>＋る→Ｖる</t>
+    </r>
+  </si>
+  <si>
+    <t>～います→う</t>
+  </si>
+  <si>
+    <r>
+      <t>～い</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Mincho"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ます</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Mincho"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>→う</t>
+    </r>
+  </si>
+  <si>
+    <t>～きます→く</t>
+  </si>
+  <si>
+    <t>～ぎます→ぐ</t>
+  </si>
+  <si>
+    <t>～します→す</t>
+  </si>
+  <si>
+    <t>～ちます→つ</t>
+  </si>
+  <si>
+    <t>～にます→ぬ</t>
+  </si>
+  <si>
+    <t>～みます→む</t>
+  </si>
+  <si>
+    <t>～びます→ぶ</t>
+  </si>
+  <si>
+    <t>～ります→る</t>
+  </si>
+  <si>
+    <t>私のしゅみは　N/Vること　です。</t>
+  </si>
+  <si>
+    <t>私のしゅみはまんがをよむことです。</t>
+  </si>
+  <si>
+    <t>私のしゅみはおんがくをきくことです。</t>
+  </si>
+  <si>
+    <t>あなたのしゅみは何ですか。</t>
+  </si>
+  <si>
+    <t>→ Sở thích của tôi là 「N/V」</t>
+  </si>
+  <si>
+    <t>→ Sở thích của bạn là gì?</t>
+  </si>
+  <si>
+    <t>Từ số lượng　に　Lượng từ</t>
+  </si>
+  <si>
+    <t>(Chỉ thời gian) (Số lượng/ Số lần)</t>
+  </si>
+  <si>
+    <t>Cách nói dùng để chỉ tần suất</t>
+  </si>
+  <si>
+    <t>一週間に一回映画がみます。</t>
+  </si>
+  <si>
+    <t>一週間に2，3冊本が読みます。</t>
+  </si>
+  <si>
+    <t>Khả năng, năng lực:</t>
+  </si>
+  <si>
+    <t>N/Vること　が　できます/できません。</t>
+  </si>
+  <si>
+    <t>毎日、食べることができます。</t>
+  </si>
+  <si>
+    <t>ミラーさんは日本語ができます。</t>
+  </si>
+  <si>
+    <t>→ Có thể (có khả năng) làm 「N/V」</t>
+  </si>
+  <si>
+    <t>なかなか～ができません。</t>
+  </si>
+  <si>
+    <t>日本でなかなかうまをみることができません。</t>
+  </si>
+  <si>
+    <t>ひらがなをかくことができますか。</t>
+  </si>
+  <si>
+    <t>ーはい、できます。</t>
+  </si>
+  <si>
+    <t>ーいいえ、できません。</t>
+  </si>
+  <si>
+    <t>N/Ｖること　が　できますか。</t>
+  </si>
+  <si>
+    <t>→ Mãi mà không thể…/ Khó mà có thể…</t>
+  </si>
+  <si>
+    <t>→ Có thể làm 「V」 không?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,12 +942,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -621,13 +949,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Mincho"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Yu Mincho"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Mincho"/>
+      <family val="1"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -702,13 +1045,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -718,8 +1057,54 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1145,943 +1530,1747 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF088B7-57DB-42FE-8A82-081056E8782F}">
-  <dimension ref="A1:D77"/>
+  <dimension ref="A2:U82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="F2" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="13"/>
+      <c r="N2" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="F3" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
+      <c r="N3" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="F4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="N4" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="F5" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="13"/>
+      <c r="N5" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="F6" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="N7" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="F8" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="N8" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="F9" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
+      <c r="N9" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="F10" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="13"/>
+      <c r="N10" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="F11" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13"/>
+      <c r="N11" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="F12" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
+      <c r="N12" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="8"/>
+      <c r="N13" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="F14" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="8"/>
+      <c r="N14" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="F15" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+      <c r="N15" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="F16" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="13"/>
+      <c r="N16" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="8"/>
+      <c r="N17" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="F18" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="8"/>
+      <c r="N18" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="F19" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="13"/>
+      <c r="N19" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="F20" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="13"/>
+      <c r="N20" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="F21" s="6"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="8"/>
+      <c r="N21" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
+      <c r="F22" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="8"/>
+      <c r="N22" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="F23" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="13"/>
+      <c r="N23" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="F24" s="6"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="8"/>
+      <c r="N24" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="F25" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+      <c r="F26" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="13"/>
+      <c r="N26" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>24</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="F27" s="6"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="8"/>
+      <c r="N27" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
         <v>25</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+      <c r="F28" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="8"/>
+      <c r="N28" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
         <v>26</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="5" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="9" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+      <c r="F29" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="13"/>
+      <c r="N29" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
         <v>27</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="9" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
+      <c r="F30" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="13"/>
+      <c r="N30" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="5" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="9" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="F31" s="6"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="8"/>
+      <c r="N31" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="5"/>
+      <c r="D32" s="9" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="F32" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="8"/>
+      <c r="N32" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
         <v>29</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="5"/>
+      <c r="D33" s="9" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
+      <c r="F33" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="13"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="5" t="s">
+      <c r="C34" s="5"/>
+      <c r="D34" s="9" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+      <c r="F34" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="13"/>
+      <c r="N34" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
         <v>30</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="9" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="F35" s="6"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="8"/>
+      <c r="N35" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="9">
         <v>31</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="5" t="s">
+      <c r="C36" s="5"/>
+      <c r="D36" s="9" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="F36" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="8"/>
+      <c r="N36" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
         <v>32</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="5"/>
+      <c r="D37" s="9" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+      <c r="F37" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="13"/>
+      <c r="N37" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F38" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="13"/>
+      <c r="N38" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F39" s="6"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="8"/>
+      <c r="N39" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="F40" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="8"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="5">
         <v>1</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="F41" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="13"/>
+      <c r="N41" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
         <v>2</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="4" t="s">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+      <c r="F42" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="13"/>
+      <c r="N42" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
         <v>3</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+      <c r="F43" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="13"/>
+      <c r="N43" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
         <v>4</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="4" t="s">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+      <c r="F44" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="13"/>
+      <c r="N44" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
         <v>5</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="4" t="s">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="F45" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="13"/>
+      <c r="N45" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
         <v>6</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="4" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
+      <c r="F46" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="13"/>
+      <c r="N46" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="4" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+      <c r="N47" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
         <v>7</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="4" t="s">
+      <c r="C49" s="5"/>
+      <c r="D49" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+      <c r="N49" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
         <v>8</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+      <c r="N50" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="O50" s="19"/>
+      <c r="P50" s="19"/>
+      <c r="Q50" s="19"/>
+      <c r="R50" s="19"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
         <v>9</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+      <c r="N51" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
         <v>10</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
+      <c r="N52" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="4" t="s">
+      <c r="C53" s="5"/>
+      <c r="D53" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
         <v>11</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
+      <c r="N54" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A55" s="5">
         <v>12</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="4" t="s">
+      <c r="C55" s="5"/>
+      <c r="D55" s="5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
+      <c r="N55" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="4" t="s">
+      <c r="C56" s="5"/>
+      <c r="D56" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+      <c r="N56" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A57" s="5">
         <v>13</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
+      <c r="N57" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
         <v>14</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="4" t="s">
+      <c r="C58" s="5"/>
+      <c r="D58" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
+      <c r="N58" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A59" s="5">
         <v>15</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="4" t="s">
+      <c r="C59" s="5"/>
+      <c r="D59" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
+      <c r="N59" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
         <v>16</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="9" t="s">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N62" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A63" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="N63" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="20"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
         <v>1</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
+      <c r="N64" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="O64" s="21"/>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="21"/>
+      <c r="R64" s="21"/>
+      <c r="S64" s="21"/>
+      <c r="T64" s="21"/>
+      <c r="U64" s="21"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A65" s="5">
         <v>2</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="4" t="s">
+      <c r="C65" s="5"/>
+      <c r="D65" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2" t="s">
+      <c r="N65" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="20"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
+      <c r="N66" s="21"/>
+      <c r="O66" s="21"/>
+      <c r="P66" s="21"/>
+      <c r="Q66" s="21"/>
+      <c r="R66" s="21"/>
+      <c r="S66" s="21"/>
+      <c r="T66" s="21"/>
+      <c r="U66" s="21"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A67" s="5">
         <v>3</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
+      <c r="N67" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="20"/>
+      <c r="R67" s="20"/>
+      <c r="S67" s="20"/>
+      <c r="T67" s="20"/>
+      <c r="U67" s="21"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A68" s="5">
         <v>4</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
+      <c r="N68" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A69" s="5">
         <v>5</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
+      <c r="N69" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="22"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A70" s="5">
         <v>6</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="21"/>
+      <c r="R70" s="21"/>
+      <c r="S70" s="21"/>
+      <c r="T70" s="21"/>
+      <c r="U70" s="21"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A71" s="5">
         <v>7</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
+      <c r="N71" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="O71" s="21"/>
+      <c r="P71" s="21"/>
+      <c r="Q71" s="21"/>
+      <c r="R71" s="21"/>
+      <c r="S71" s="21"/>
+      <c r="T71" s="21"/>
+      <c r="U71" s="21"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A72" s="5">
         <v>8</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
+      <c r="N72" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="O72" s="21"/>
+      <c r="P72" s="21"/>
+      <c r="Q72" s="21"/>
+      <c r="R72" s="21"/>
+      <c r="S72" s="21"/>
+      <c r="T72" s="21"/>
+      <c r="U72" s="21"/>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A73" s="5">
         <v>9</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
+      <c r="N73" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="O73" s="21"/>
+      <c r="P73" s="21"/>
+      <c r="Q73" s="21"/>
+      <c r="R73" s="21"/>
+      <c r="S73" s="21"/>
+      <c r="T73" s="21"/>
+      <c r="U73" s="21"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A74" s="5">
         <v>10</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
+      <c r="P74" s="21"/>
+      <c r="Q74" s="21"/>
+      <c r="R74" s="21"/>
+      <c r="S74" s="21"/>
+      <c r="T74" s="21"/>
+      <c r="U74" s="21"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A75" s="5">
         <v>11</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
+      <c r="N75" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="O75" s="20"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="20"/>
+      <c r="U75" s="20"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A76" s="5">
         <v>12</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
+      <c r="N76" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="O76" s="20"/>
+      <c r="P76" s="20"/>
+      <c r="Q76" s="20"/>
+      <c r="R76" s="20"/>
+      <c r="S76" s="20"/>
+      <c r="T76" s="20"/>
+      <c r="U76" s="20"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A77" s="5">
         <v>13</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C77" s="2"/>
-      <c r="D77" s="4" t="s">
+      <c r="C77" s="5"/>
+      <c r="D77" s="5" t="s">
         <v>73</v>
       </c>
+      <c r="N77" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="O77" s="20"/>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
+      <c r="R77" s="20"/>
+      <c r="S77" s="20"/>
+      <c r="T77" s="20"/>
+      <c r="U77" s="20"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N78" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="O78" s="21"/>
+      <c r="P78" s="21"/>
+      <c r="Q78" s="21"/>
+      <c r="R78" s="21"/>
+      <c r="S78" s="21"/>
+      <c r="T78" s="21"/>
+      <c r="U78" s="21"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N79" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="O79" s="23"/>
+      <c r="P79" s="23"/>
+      <c r="Q79" s="23"/>
+      <c r="R79" s="23"/>
+      <c r="S79" s="23"/>
+      <c r="T79" s="23"/>
+      <c r="U79" s="23"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N80" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="O80" s="20"/>
+      <c r="P80" s="20"/>
+      <c r="Q80" s="20"/>
+      <c r="R80" s="20"/>
+      <c r="S80" s="20"/>
+      <c r="T80" s="20"/>
+      <c r="U80" s="20"/>
+    </row>
+    <row r="81" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="N81" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="O81" s="20"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="20"/>
+      <c r="U81" s="20"/>
+    </row>
+    <row r="82" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="N82" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="O82" s="20"/>
+      <c r="P82" s="20"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="49">
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="F45:L45"/>
+    <mergeCell ref="F46:L46"/>
+    <mergeCell ref="F39:L39"/>
+    <mergeCell ref="F35:L35"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="F37:L37"/>
+    <mergeCell ref="F38:L38"/>
+    <mergeCell ref="F30:L30"/>
+    <mergeCell ref="F41:L41"/>
+    <mergeCell ref="F42:L42"/>
+    <mergeCell ref="F44:L44"/>
+    <mergeCell ref="F43:L43"/>
+    <mergeCell ref="F31:L31"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="F34:L34"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="F26:L26"/>
+    <mergeCell ref="F27:L27"/>
+    <mergeCell ref="H28:L28"/>
+    <mergeCell ref="F29:L29"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="F21:L21"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="F23:L23"/>
+    <mergeCell ref="F24:L24"/>
+    <mergeCell ref="F15:L15"/>
+    <mergeCell ref="F16:L16"/>
+    <mergeCell ref="F17:L17"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="F19:L19"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="F13:L13"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F6:L6"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="F2:L2"/>
+    <mergeCell ref="F7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="F9:L9"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/JPD/documents/full_jpd.xlsx
+++ b/JPD/documents/full_jpd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\JPD\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/fptu/JPD/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AEBFF2-6DC4-4DFB-AFFF-794440E86681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000E7DAC-5AA6-E844-9A49-B44A3058DE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="9" xr2:uid="{FA3ADD2E-6701-4EA2-BF3C-245AE1375C42}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="13440" windowHeight="17220" firstSheet="3" activeTab="7" xr2:uid="{FA3ADD2E-6701-4EA2-BF3C-245AE1375C42}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="805">
   <si>
     <t>イベント</t>
   </si>
@@ -2544,6 +2544,15 @@
   </si>
   <si>
     <t>ここでたばごをすってもいいですか。</t>
+  </si>
+  <si>
+    <t>起 KHỞI</t>
+  </si>
+  <si>
+    <t>起きる　「おきる」　thức dậy</t>
+  </si>
+  <si>
+    <t>起こす　「おこす」　đánh thức, gây ra</t>
   </si>
 </sst>
 </file>
@@ -2714,31 +2723,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2748,20 +2752,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2772,6 +2770,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2780,24 +2799,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2817,18 +2818,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3165,7 +3166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F32A665-E04D-42CB-B78D-58004897372A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3174,153 +3175,153 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9EDDB9E-D9C0-4B8D-AA06-739DDD26025B}">
   <dimension ref="A2:AC82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="41" style="1" customWidth="1"/>
-    <col min="5" max="12" width="8.88671875" style="1"/>
-    <col min="13" max="13" width="15.88671875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="12" width="8.83203125" style="1"/>
+    <col min="13" max="13" width="15.83203125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
         <v>263</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
       <c r="F2" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="48"/>
-      <c r="W3" s="26" t="s">
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="23"/>
+      <c r="W3" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="28"/>
-    </row>
-    <row r="4" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="21"/>
+    </row>
+    <row r="4" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="7" t="s">
         <v>270</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="22" t="s">
         <v>315</v>
       </c>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
       <c r="W4" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="21"/>
-    </row>
-    <row r="5" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X4" s="14"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="16"/>
+    </row>
+    <row r="5" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="7" t="s">
         <v>271</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="W5" s="26" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="W5" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="28"/>
-    </row>
-    <row r="6" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="21"/>
+    </row>
+    <row r="6" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="7" t="s">
         <v>272</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="W6" s="26" t="s">
+      <c r="W6" s="19" t="s">
         <v>796</v>
       </c>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="27"/>
-      <c r="AC6" s="28"/>
-    </row>
-    <row r="7" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="21"/>
+    </row>
+    <row r="7" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="7" t="s">
         <v>274</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -3329,15 +3330,15 @@
       <c r="F7" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="W7" s="16"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="17"/>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="18"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="W7" s="11"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="13"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -3351,17 +3352,17 @@
       <c r="F8" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="21"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X8" s="14"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="15"/>
+      <c r="AC8" s="16"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -3375,17 +3376,17 @@
       <c r="F9" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="W9" s="26" t="s">
+      <c r="W9" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="28"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -3396,24 +3397,24 @@
       <c r="D10" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="W10" s="26" t="s">
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="W10" s="19" t="s">
         <v>797</v>
       </c>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="27"/>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="28"/>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -3424,22 +3425,22 @@
       <c r="D11" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F11" s="45" t="s">
+      <c r="F11" s="22" t="s">
         <v>318</v>
       </c>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="18"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12"/>
+      <c r="AB11" s="12"/>
+      <c r="AC11" s="13"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -3450,43 +3451,43 @@
       <c r="D12" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="W12" s="4" t="s">
+      <c r="W12" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="21"/>
-    </row>
-    <row r="13" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X12" s="14"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="16"/>
+    </row>
+    <row r="13" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="8" t="s">
         <v>301</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="W13" s="26" t="s">
+      <c r="W13" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="28"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="21"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -3500,17 +3501,17 @@
       <c r="F14" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="W14" s="26" t="s">
+      <c r="W14" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="27"/>
-      <c r="AB14" s="27"/>
-      <c r="AC14" s="28"/>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="21"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -3524,17 +3525,17 @@
       <c r="F15" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="W15" s="26" t="s">
+      <c r="W15" s="19" t="s">
         <v>798</v>
       </c>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="27"/>
-      <c r="Z15" s="27"/>
-      <c r="AA15" s="27"/>
-      <c r="AB15" s="27"/>
-      <c r="AC15" s="28"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="21"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -3548,30 +3549,30 @@
       <c r="F16" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="W16" s="16"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17"/>
-      <c r="AA16" s="17"/>
-      <c r="AB16" s="17"/>
-      <c r="AC16" s="18"/>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="W16" s="11"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
+      <c r="AA16" s="12"/>
+      <c r="AB16" s="12"/>
+      <c r="AC16" s="13"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="W17" s="4" t="s">
+      <c r="W17" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="21"/>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X17" s="14"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="16"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -3582,23 +3583,23 @@
       <c r="D18" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F18" s="45" t="s">
+      <c r="F18" s="22" t="s">
         <v>323</v>
       </c>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="W18" s="26" t="s">
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="W18" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="X18" s="27"/>
-      <c r="Y18" s="27"/>
-      <c r="Z18" s="27"/>
-      <c r="AA18" s="27"/>
-      <c r="AB18" s="27"/>
-      <c r="AC18" s="28"/>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="21"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -3609,23 +3610,23 @@
       <c r="D19" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F19" s="45" t="s">
+      <c r="F19" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="W19" s="26" t="s">
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="W19" s="19" t="s">
         <v>799</v>
       </c>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="27"/>
-      <c r="AB19" s="27"/>
-      <c r="AC19" s="28"/>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="21"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -3636,15 +3637,15 @@
       <c r="D20" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="W20" s="16"/>
-      <c r="X20" s="17"/>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="17"/>
-      <c r="AA20" s="17"/>
-      <c r="AB20" s="17"/>
-      <c r="AC20" s="18"/>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="W20" s="11"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="12"/>
+      <c r="AC20" s="13"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -3658,17 +3659,17 @@
       <c r="F21" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="W21" s="4" t="s">
+      <c r="W21" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="21"/>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X21" s="14"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15"/>
+      <c r="AB21" s="15"/>
+      <c r="AC21" s="16"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -3682,38 +3683,38 @@
       <c r="F22" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="W22" s="26" t="s">
+      <c r="W22" s="19" t="s">
         <v>800</v>
       </c>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="27"/>
-      <c r="Z22" s="27"/>
-      <c r="AA22" s="27"/>
-      <c r="AB22" s="27"/>
-      <c r="AC22" s="28"/>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="21"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
         <v>20</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="W23" s="26" t="s">
+      <c r="W23" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="28"/>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="21"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -3727,97 +3728,89 @@
       <c r="F24" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="W24" s="22"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="23"/>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="5"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="18"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="F25" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="W25" s="4" t="s">
+      <c r="W25" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="21"/>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="W26" s="26" t="s">
+      <c r="X25" s="14"/>
+      <c r="Y25" s="15"/>
+      <c r="Z25" s="15"/>
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="15"/>
+      <c r="AC25" s="16"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="W26" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
-      <c r="AC26" s="28"/>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A27" s="35" t="s">
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="21"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
         <v>329</v>
       </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
       <c r="F27" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="W27" s="26" t="s">
+      <c r="W27" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-      <c r="AA27" s="27"/>
-      <c r="AB27" s="27"/>
-      <c r="AC27" s="28"/>
-    </row>
-    <row r="28" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="21"/>
+    </row>
+    <row r="28" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="7" t="s">
         <v>338</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="W28" s="26" t="s">
+      <c r="W28" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="28"/>
-    </row>
-    <row r="29" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="21"/>
+    </row>
+    <row r="29" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>2</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7" t="s">
         <v>331</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -3826,22 +3819,22 @@
       <c r="F29" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="W29" s="26" t="s">
+      <c r="W29" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="28"/>
-    </row>
-    <row r="30" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="21"/>
+    </row>
+    <row r="30" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>3</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10" t="s">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7" t="s">
         <v>332</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -3850,15 +3843,15 @@
       <c r="F30" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="W30" s="22"/>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="6"/>
-      <c r="AB30" s="6"/>
-      <c r="AC30" s="23"/>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="W30" s="17"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="5"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="18"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>4</v>
       </c>
@@ -3874,22 +3867,22 @@
       <c r="F31" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="W31" s="4" t="s">
+      <c r="W31" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="21"/>
-    </row>
-    <row r="32" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X31" s="14"/>
+      <c r="Y31" s="15"/>
+      <c r="Z31" s="15"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="15"/>
+      <c r="AC31" s="16"/>
+    </row>
+    <row r="32" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>5</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="7" t="s">
         <v>333</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -3898,39 +3891,39 @@
       <c r="F32" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="W32" s="26" t="s">
+      <c r="W32" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
-      <c r="AC32" s="28"/>
-    </row>
-    <row r="33" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="21"/>
+    </row>
+    <row r="33" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>6</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="2" t="s">
         <v>345</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="W33" s="16"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
-      <c r="Z33" s="17"/>
-      <c r="AA33" s="17"/>
-      <c r="AB33" s="17"/>
-      <c r="AC33" s="18"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="W33" s="11"/>
+      <c r="X33" s="12"/>
+      <c r="Y33" s="12"/>
+      <c r="Z33" s="12"/>
+      <c r="AA33" s="12"/>
+      <c r="AB33" s="12"/>
+      <c r="AC33" s="13"/>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>7</v>
       </c>
@@ -3944,17 +3937,17 @@
       <c r="F34" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="W34" s="4" t="s">
+      <c r="W34" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="20"/>
-      <c r="Z34" s="20"/>
-      <c r="AA34" s="20"/>
-      <c r="AB34" s="20"/>
-      <c r="AC34" s="21"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X34" s="14"/>
+      <c r="Y34" s="15"/>
+      <c r="Z34" s="15"/>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="15"/>
+      <c r="AC34" s="16"/>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>8</v>
       </c>
@@ -3965,17 +3958,17 @@
       <c r="D35" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="W35" s="26" t="s">
+      <c r="W35" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="X35" s="27"/>
-      <c r="Y35" s="27"/>
-      <c r="Z35" s="27"/>
-      <c r="AA35" s="27"/>
-      <c r="AB35" s="27"/>
-      <c r="AC35" s="28"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="21"/>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>9</v>
       </c>
@@ -3986,23 +3979,23 @@
       <c r="D36" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F36" s="45" t="s">
+      <c r="F36" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="W36" s="26" t="s">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="W36" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="X36" s="27"/>
-      <c r="Y36" s="27"/>
-      <c r="Z36" s="27"/>
-      <c r="AA36" s="27"/>
-      <c r="AB36" s="27"/>
-      <c r="AC36" s="28"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
+      <c r="AC36" s="21"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>10</v>
       </c>
@@ -4013,39 +4006,39 @@
       <c r="D37" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="W37" s="22"/>
-      <c r="X37" s="6"/>
-      <c r="Y37" s="6"/>
-      <c r="Z37" s="6"/>
-      <c r="AA37" s="6"/>
-      <c r="AB37" s="6"/>
-      <c r="AC37" s="23"/>
-    </row>
-    <row r="38" spans="1:29" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="W37" s="17"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
+      <c r="AA37" s="5"/>
+      <c r="AB37" s="5"/>
+      <c r="AC37" s="18"/>
+    </row>
+    <row r="38" spans="1:29" ht="20" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>11</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="11" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="8" t="s">
         <v>362</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="W38" s="4" t="s">
+      <c r="W38" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="X38" s="19"/>
-      <c r="Y38" s="20"/>
-      <c r="Z38" s="20"/>
-      <c r="AA38" s="20"/>
-      <c r="AB38" s="20"/>
-      <c r="AC38" s="21"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X38" s="14"/>
+      <c r="Y38" s="15"/>
+      <c r="Z38" s="15"/>
+      <c r="AA38" s="15"/>
+      <c r="AB38" s="15"/>
+      <c r="AC38" s="16"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>12</v>
       </c>
@@ -4059,17 +4052,17 @@
       <c r="F39" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="W39" s="26" t="s">
+      <c r="W39" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
-      <c r="AA39" s="27"/>
-      <c r="AB39" s="27"/>
-      <c r="AC39" s="28"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="21"/>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>13</v>
       </c>
@@ -4083,39 +4076,39 @@
       <c r="F40" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="W40" s="26" t="s">
+      <c r="W40" s="19" t="s">
         <v>425</v>
       </c>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="28"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="20"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="21"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="15" t="s">
+      <c r="C41" s="20"/>
+      <c r="D41" s="2" t="s">
         <v>365</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="W41" s="26" t="s">
+      <c r="W41" s="19" t="s">
         <v>426</v>
       </c>
-      <c r="X41" s="27"/>
-      <c r="Y41" s="27"/>
-      <c r="Z41" s="27"/>
-      <c r="AA41" s="27"/>
-      <c r="AB41" s="27"/>
-      <c r="AC41" s="28"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="21"/>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>14</v>
       </c>
@@ -4129,17 +4122,17 @@
       <c r="F42" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="W42" s="26" t="s">
+      <c r="W42" s="19" t="s">
         <v>427</v>
       </c>
-      <c r="X42" s="27"/>
-      <c r="Y42" s="27"/>
-      <c r="Z42" s="27"/>
-      <c r="AA42" s="27"/>
-      <c r="AB42" s="27"/>
-      <c r="AC42" s="28"/>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="20"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
+      <c r="AC42" s="21"/>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>15</v>
       </c>
@@ -4153,15 +4146,15 @@
       <c r="F43" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>16</v>
       </c>
@@ -4175,15 +4168,15 @@
       <c r="F44" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>17</v>
       </c>
@@ -4197,15 +4190,15 @@
       <c r="F45" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>18</v>
       </c>
@@ -4219,15 +4212,15 @@
       <c r="F46" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>19</v>
       </c>
@@ -4241,15 +4234,15 @@
       <c r="F47" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>20</v>
       </c>
@@ -4263,15 +4256,15 @@
       <c r="F48" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>21</v>
       </c>
@@ -4286,47 +4279,47 @@
         <v>388</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F50" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F51" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="35" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
       <c r="F52" s="1" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="20" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>1</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="7" t="s">
         <v>429</v>
       </c>
       <c r="C53" s="2"/>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="7" t="s">
         <v>453</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="20" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>2</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="7" t="s">
         <v>430</v>
       </c>
       <c r="C54" s="2"/>
@@ -4337,11 +4330,11 @@
         <v>393</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="20" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>3</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="7" t="s">
         <v>431</v>
       </c>
       <c r="C55" s="2"/>
@@ -4349,7 +4342,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>4</v>
       </c>
@@ -4364,12 +4357,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="20" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>5</v>
       </c>
       <c r="B57" s="2"/>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="7" t="s">
         <v>433</v>
       </c>
       <c r="D57" s="2" t="s">
@@ -4379,11 +4372,11 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="20" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>6</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="7" t="s">
         <v>434</v>
       </c>
       <c r="C58" s="2"/>
@@ -4394,7 +4387,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>7</v>
       </c>
@@ -4409,7 +4402,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>8</v>
       </c>
@@ -4423,7 +4416,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>9</v>
       </c>
@@ -4440,7 +4433,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>10</v>
       </c>
@@ -4455,22 +4448,22 @@
         <v>398</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="20" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>11</v>
       </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="11" t="s">
+      <c r="B63" s="10"/>
+      <c r="C63" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="8" t="s">
         <v>463</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>12</v>
       </c>
@@ -4485,7 +4478,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>13</v>
       </c>
@@ -4500,22 +4493,22 @@
         <v>400</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>14</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="15" t="s">
+      <c r="C66" s="3"/>
+      <c r="D66" s="2" t="s">
         <v>466</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>15</v>
       </c>
@@ -4527,7 +4520,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>16</v>
       </c>
@@ -4539,7 +4532,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>17</v>
       </c>
@@ -4554,7 +4547,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>18</v>
       </c>
@@ -4565,17 +4558,11 @@
       <c r="D70" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>19</v>
       </c>
@@ -4589,11 +4576,8 @@
       <c r="F71" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>20</v>
       </c>
@@ -4604,17 +4588,11 @@
       <c r="D72" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="F72" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>21</v>
       </c>
@@ -4625,15 +4603,8 @@
       <c r="D73" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>22</v>
       </c>
@@ -4651,7 +4622,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>23</v>
       </c>
@@ -4669,7 +4640,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>24</v>
       </c>
@@ -4683,7 +4654,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>25</v>
       </c>
@@ -4698,7 +4669,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>26</v>
       </c>
@@ -4716,7 +4687,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>27</v>
       </c>
@@ -4731,7 +4702,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>28</v>
       </c>
@@ -4749,25 +4720,20 @@
         <v>499</v>
       </c>
     </row>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F82" s="1" t="s">
         <v>495</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="W41:AC41"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="W32:AC32"/>
-    <mergeCell ref="W35:AC35"/>
-    <mergeCell ref="W36:AC36"/>
-    <mergeCell ref="W39:AC39"/>
-    <mergeCell ref="W40:AC40"/>
-    <mergeCell ref="W23:AC23"/>
-    <mergeCell ref="W26:AC26"/>
-    <mergeCell ref="W27:AC27"/>
-    <mergeCell ref="W28:AC28"/>
-    <mergeCell ref="W29:AC29"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="W42:AC42"/>
     <mergeCell ref="W3:AC3"/>
     <mergeCell ref="F5:K5"/>
@@ -4784,13 +4750,18 @@
     <mergeCell ref="W18:AC18"/>
     <mergeCell ref="W19:AC19"/>
     <mergeCell ref="W22:AC22"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="W41:AC41"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="W32:AC32"/>
+    <mergeCell ref="W35:AC35"/>
+    <mergeCell ref="W36:AC36"/>
+    <mergeCell ref="W39:AC39"/>
+    <mergeCell ref="W40:AC40"/>
+    <mergeCell ref="W23:AC23"/>
+    <mergeCell ref="W26:AC26"/>
+    <mergeCell ref="W27:AC27"/>
+    <mergeCell ref="W28:AC28"/>
+    <mergeCell ref="W29:AC29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4798,9 +4769,103 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7715BC0D-203D-45A4-B13D-55CAA00FE3B4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="N2:T9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="14:20" ht="18" x14ac:dyDescent="0.2">
+      <c r="N2" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="21"/>
+    </row>
+    <row r="3" spans="14:20" ht="18" x14ac:dyDescent="0.25">
+      <c r="N3" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="O3" s="14"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="16"/>
+    </row>
+    <row r="4" spans="14:20" ht="18" x14ac:dyDescent="0.2">
+      <c r="N4" s="19" t="s">
+        <v>803</v>
+      </c>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+    </row>
+    <row r="5" spans="14:20" ht="18" x14ac:dyDescent="0.2">
+      <c r="N5" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="21"/>
+    </row>
+    <row r="6" spans="14:20" ht="18" x14ac:dyDescent="0.2">
+      <c r="N6" s="11"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="13"/>
+    </row>
+    <row r="7" spans="14:20" ht="18" x14ac:dyDescent="0.25">
+      <c r="N7" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="O7" s="14"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="16"/>
+    </row>
+    <row r="8" spans="14:20" ht="18" x14ac:dyDescent="0.2">
+      <c r="N8" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="21"/>
+    </row>
+    <row r="9" spans="14:20" ht="18" x14ac:dyDescent="0.2">
+      <c r="N9" s="19" t="s">
+        <v>797</v>
+      </c>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="N2:T2"/>
+    <mergeCell ref="N4:T4"/>
+    <mergeCell ref="N5:T5"/>
+    <mergeCell ref="N8:T8"/>
+    <mergeCell ref="N9:T9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4808,7 +4873,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176D6F43-4DEE-4094-82FF-D8D102B92DD6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4817,7 +4882,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038D9E9F-1E5C-4220-97E7-ECFF2BC39575}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4826,7 +4891,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C2745B-D559-4802-92E7-35BBE65B093C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4835,7 +4900,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A24781D3-F2BB-4433-AA9E-D1F5D686529D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4844,7 +4909,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F55137A-32AE-4261-8F87-15B964CC16E9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4853,7 +4918,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA3F567-5202-4EAF-99BB-F578549F59EB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4862,192 +4927,192 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7146DB20-849B-4D64-AAEE-F4A38081F2FE}">
   <dimension ref="A2:U101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="23.44140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="26.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="1"/>
+    <col min="6" max="6" width="23.5" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
         <v>566</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="F2" s="26" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="F2" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="28"/>
-      <c r="O2" s="45" t="s">
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="O2" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-    </row>
-    <row r="3" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+    </row>
+    <row r="3" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="39" t="s">
         <v>674</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="31"/>
-      <c r="O3" s="44" t="s">
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="O3" s="25" t="s">
         <v>718</v>
       </c>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-    </row>
-    <row r="4" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+    </row>
+    <row r="4" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7" t="s">
         <v>501</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="38" t="s">
         <v>676</v>
       </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="28"/>
-      <c r="O4" s="44" t="s">
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="O4" s="25" t="s">
         <v>719</v>
       </c>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-    </row>
-    <row r="5" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+    </row>
+    <row r="5" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
         <v>502</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="38" t="s">
         <v>677</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="28"/>
-      <c r="O5" s="44" t="s">
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="O5" s="25" t="s">
         <v>722</v>
       </c>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-    </row>
-    <row r="6" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+    </row>
+    <row r="6" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="7" t="s">
         <v>503</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="28"/>
-      <c r="O6" s="44" t="s">
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="O6" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-    </row>
-    <row r="7" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+    </row>
+    <row r="7" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
         <v>504</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="39" t="s">
         <v>675</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="31"/>
-      <c r="O7" s="44" t="s">
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="O7" s="25" t="s">
         <v>720</v>
       </c>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -5058,26 +5123,26 @@
       <c r="D8" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="38" t="s">
         <v>678</v>
       </c>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="28"/>
-      <c r="O8" s="44" t="s">
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="O8" s="25" t="s">
         <v>721</v>
       </c>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -5088,13 +5153,13 @@
       <c r="D9" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="28"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
@@ -5103,7 +5168,7 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -5114,26 +5179,26 @@
       <c r="D10" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="39" t="s">
         <v>679</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="31"/>
-      <c r="O10" s="44" t="s">
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="O10" s="25" t="s">
         <v>723</v>
       </c>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -5144,26 +5209,26 @@
       <c r="D11" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="38" t="s">
         <v>680</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="28"/>
-      <c r="O11" s="44" t="s">
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="O11" s="25" t="s">
         <v>729</v>
       </c>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -5174,54 +5239,54 @@
       <c r="D12" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="38" t="s">
         <v>681</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="28"/>
-      <c r="O12" s="44" t="s">
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="O12" s="25" t="s">
         <v>723</v>
       </c>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-    </row>
-    <row r="13" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+    </row>
+    <row r="13" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="11" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="31"/>
-      <c r="O13" s="44" t="s">
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="O13" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -5232,26 +5297,26 @@
       <c r="D14" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="39" t="s">
         <v>682</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="31"/>
-      <c r="O14" s="44" t="s">
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="O14" s="25" t="s">
         <v>724</v>
       </c>
-      <c r="P14" s="44"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="44"/>
-      <c r="S14" s="44"/>
-      <c r="T14" s="44"/>
-      <c r="U14" s="44"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -5262,26 +5327,26 @@
       <c r="D15" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="38" t="s">
         <v>683</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="28"/>
-      <c r="O15" s="44" t="s">
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="O15" s="25" t="s">
         <v>725</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="44"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -5292,15 +5357,15 @@
       <c r="D16" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="38" t="s">
         <v>684</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="28"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
@@ -5309,7 +5374,7 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -5320,26 +5385,26 @@
       <c r="D17" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="38" t="s">
         <v>685</v>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="28"/>
-      <c r="O17" s="44" t="s">
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="O17" s="25" t="s">
         <v>726</v>
       </c>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="44"/>
-      <c r="R17" s="44"/>
-      <c r="S17" s="44"/>
-      <c r="T17" s="44"/>
-      <c r="U17" s="44"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -5350,26 +5415,26 @@
       <c r="D18" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="38" t="s">
         <v>686</v>
       </c>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="28"/>
-      <c r="O18" s="44" t="s">
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="O18" s="25" t="s">
         <v>730</v>
       </c>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="44"/>
-      <c r="S18" s="44"/>
-      <c r="T18" s="44"/>
-      <c r="U18" s="44"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -5380,24 +5445,24 @@
       <c r="D19" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="F19" s="26"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
-      <c r="O19" s="44" t="s">
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="O19" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -5408,26 +5473,26 @@
       <c r="D20" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="39" t="s">
         <v>687</v>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="31"/>
-      <c r="O20" s="44" t="s">
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="O20" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="44"/>
-      <c r="T20" s="44"/>
-      <c r="U20" s="44"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -5438,26 +5503,26 @@
       <c r="D21" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="38" t="s">
         <v>688</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="28"/>
-      <c r="O21" s="44" t="s">
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="O21" s="25" t="s">
         <v>728</v>
       </c>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
-      <c r="U21" s="44"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -5468,15 +5533,15 @@
       <c r="D22" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="38" t="s">
         <v>689</v>
       </c>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="28"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
@@ -5485,7 +5550,7 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -5496,24 +5561,24 @@
       <c r="D23" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="28"/>
-      <c r="O23" s="44" t="s">
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="O23" s="25" t="s">
         <v>731</v>
       </c>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="44"/>
-      <c r="T23" s="44"/>
-      <c r="U23" s="44"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -5524,17 +5589,17 @@
       <c r="D24" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="39" t="s">
         <v>690</v>
       </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="31"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -5545,274 +5610,274 @@
       <c r="D25" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="38" t="s">
         <v>691</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="28"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>536</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="38" t="s">
         <v>692</v>
       </c>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="28"/>
-      <c r="O26" s="44" t="s">
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="O26" s="25" t="s">
         <v>732</v>
       </c>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44"/>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>537</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="F27" s="38" t="s">
         <v>693</v>
       </c>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="28"/>
-      <c r="O27" s="44" t="s">
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="O27" s="25" t="s">
         <v>733</v>
       </c>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="44"/>
-      <c r="T27" s="44"/>
-      <c r="U27" s="44"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>26</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>538</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="F28" s="32"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="34"/>
-      <c r="O28" s="44" t="s">
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="O28" s="25" t="s">
         <v>746</v>
       </c>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>539</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="39" t="s">
         <v>694</v>
       </c>
-      <c r="G29" s="29"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="31"/>
-      <c r="O29" s="44" t="s">
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="O29" s="25" t="s">
         <v>734</v>
       </c>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="44"/>
-      <c r="U29" s="44"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>540</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="38" t="s">
         <v>695</v>
       </c>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="28"/>
-      <c r="O30" s="44" t="s">
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="O30" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
-      <c r="U30" s="44"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>562</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="38" t="s">
         <v>696</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="28"/>
-      <c r="O31" s="44" t="s">
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="O31" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
-      <c r="S31" s="44"/>
-      <c r="T31" s="44"/>
-      <c r="U31" s="44"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="19" t="s">
         <v>563</v>
       </c>
-      <c r="C32" s="28"/>
+      <c r="C32" s="21"/>
       <c r="D32" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="F32" s="32"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="34"/>
-      <c r="O32" s="44" t="s">
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="O32" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="44"/>
-      <c r="T32" s="44"/>
-      <c r="U32" s="44"/>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="C33" s="3"/>
+      <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="39" t="s">
         <v>697</v>
       </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="31"/>
-      <c r="O33" s="44" t="s">
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="40"/>
+      <c r="O33" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="44"/>
-      <c r="S33" s="44"/>
-      <c r="T33" s="44"/>
-      <c r="U33" s="44"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>716</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="F34" s="46"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="25"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
@@ -5821,208 +5886,208 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="19" t="s">
         <v>541</v>
       </c>
-      <c r="C35" s="28"/>
+      <c r="C35" s="21"/>
       <c r="D35" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="38" t="s">
         <v>698</v>
       </c>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="28"/>
-      <c r="O35" s="44" t="s">
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="O35" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="P35" s="44"/>
-      <c r="Q35" s="44"/>
-      <c r="R35" s="44"/>
-      <c r="S35" s="44"/>
-      <c r="T35" s="44"/>
-      <c r="U35" s="44"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="F36" s="26" t="s">
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F36" s="38" t="s">
         <v>699</v>
       </c>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="28"/>
-      <c r="O36" s="44" t="s">
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="O36" s="25" t="s">
         <v>747</v>
       </c>
-      <c r="P36" s="44"/>
-      <c r="Q36" s="44"/>
-      <c r="R36" s="44"/>
-      <c r="S36" s="44"/>
-      <c r="T36" s="44"/>
-      <c r="U36" s="44"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="F37" s="26" t="s">
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F37" s="38" t="s">
         <v>700</v>
       </c>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="28"/>
-      <c r="O37" s="44" t="s">
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="O37" s="25" t="s">
         <v>739</v>
       </c>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="44"/>
-      <c r="R37" s="44"/>
-      <c r="S37" s="44"/>
-      <c r="T37" s="44"/>
-      <c r="U37" s="44"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="35" t="s">
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="25"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
         <v>565</v>
       </c>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
-      <c r="O38" s="44" t="s">
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="O38" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="P38" s="44"/>
-      <c r="Q38" s="44"/>
-      <c r="R38" s="44"/>
-      <c r="S38" s="44"/>
-      <c r="T38" s="44"/>
-      <c r="U38" s="44"/>
-    </row>
-    <row r="39" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="25"/>
+      <c r="S38" s="25"/>
+      <c r="T38" s="25"/>
+      <c r="U38" s="25"/>
+    </row>
+    <row r="39" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>1</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="39" t="s">
         <v>701</v>
       </c>
-      <c r="G39" s="29"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="31"/>
-      <c r="O39" s="44" t="s">
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="O39" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P39" s="44"/>
-      <c r="Q39" s="44"/>
-      <c r="R39" s="44"/>
-      <c r="S39" s="44"/>
-      <c r="T39" s="44"/>
-      <c r="U39" s="44"/>
-    </row>
-    <row r="40" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P39" s="25"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+    </row>
+    <row r="40" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>2</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10" t="s">
+      <c r="B40" s="7"/>
+      <c r="C40" s="7" t="s">
         <v>568</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="F40" s="26" t="s">
+      <c r="F40" s="38" t="s">
         <v>702</v>
       </c>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="28"/>
-      <c r="O40" s="44" t="s">
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="O40" s="25" t="s">
         <v>741</v>
       </c>
-      <c r="P40" s="44"/>
-      <c r="Q40" s="44"/>
-      <c r="R40" s="44"/>
-      <c r="S40" s="44"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
-    </row>
-    <row r="41" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P40" s="25"/>
+      <c r="Q40" s="25"/>
+      <c r="R40" s="25"/>
+      <c r="S40" s="25"/>
+      <c r="T40" s="25"/>
+      <c r="U40" s="25"/>
+    </row>
+    <row r="41" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>3</v>
       </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10" t="s">
+      <c r="B41" s="7"/>
+      <c r="C41" s="7" t="s">
         <v>569</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="F41" s="26"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="28"/>
-      <c r="O41" s="44" t="s">
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
+      <c r="O41" s="25" t="s">
         <v>742</v>
       </c>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="44"/>
-      <c r="T41" s="44"/>
-      <c r="U41" s="44"/>
-    </row>
-    <row r="42" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P41" s="25"/>
+      <c r="Q41" s="25"/>
+      <c r="R41" s="25"/>
+      <c r="S41" s="25"/>
+      <c r="T41" s="25"/>
+      <c r="U41" s="25"/>
+    </row>
+    <row r="42" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>4</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="7" t="s">
         <v>570</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="39" t="s">
         <v>703</v>
       </c>
-      <c r="G42" s="29"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="31"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="40"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
@@ -6031,37 +6096,37 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
     </row>
-    <row r="43" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>5</v>
       </c>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10" t="s">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7" t="s">
         <v>571</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="38" t="s">
         <v>704</v>
       </c>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="28"/>
-      <c r="O43" s="44" t="s">
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="O43" s="25" t="s">
         <v>743</v>
       </c>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="44"/>
-      <c r="R43" s="44"/>
-      <c r="S43" s="44"/>
-      <c r="T43" s="44"/>
-      <c r="U43" s="44"/>
-    </row>
-    <row r="44" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P43" s="25"/>
+      <c r="Q43" s="25"/>
+      <c r="R43" s="25"/>
+      <c r="S43" s="25"/>
+      <c r="T43" s="25"/>
+      <c r="U43" s="25"/>
+    </row>
+    <row r="44" spans="1:21" ht="16.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>6</v>
       </c>
@@ -6072,26 +6137,26 @@
       <c r="D44" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F44" s="26" t="s">
+      <c r="F44" s="38" t="s">
         <v>705</v>
       </c>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="28"/>
-      <c r="O44" s="47" t="s">
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
+      <c r="O44" s="26" t="s">
         <v>748</v>
       </c>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="47"/>
-      <c r="U44" s="47"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P44" s="26"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
+      <c r="T44" s="26"/>
+      <c r="U44" s="26"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>7</v>
       </c>
@@ -6102,26 +6167,26 @@
       <c r="D45" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="F45" s="26" t="s">
+      <c r="F45" s="38" t="s">
         <v>706</v>
       </c>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="28"/>
-      <c r="O45" s="47" t="s">
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="38"/>
+      <c r="O45" s="26" t="s">
         <v>749</v>
       </c>
-      <c r="P45" s="47"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-    </row>
-    <row r="46" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P45" s="26"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="26"/>
+      <c r="S45" s="26"/>
+      <c r="T45" s="26"/>
+      <c r="U45" s="26"/>
+    </row>
+    <row r="46" spans="1:21" ht="16.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>8</v>
       </c>
@@ -6132,24 +6197,24 @@
       <c r="D46" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="F46" s="26"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="28"/>
-      <c r="O46" s="47" t="s">
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="38"/>
+      <c r="K46" s="38"/>
+      <c r="L46" s="38"/>
+      <c r="O46" s="26" t="s">
         <v>750</v>
       </c>
-      <c r="P46" s="47"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="47"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P46" s="26"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="26"/>
+      <c r="T46" s="26"/>
+      <c r="U46" s="26"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>9</v>
       </c>
@@ -6160,26 +6225,26 @@
       <c r="D47" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="39" t="s">
         <v>707</v>
       </c>
-      <c r="G47" s="29"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="31"/>
-      <c r="O47" s="44" t="s">
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+      <c r="O47" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P47" s="44"/>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="44"/>
-      <c r="S47" s="44"/>
-      <c r="T47" s="44"/>
-      <c r="U47" s="44"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P47" s="25"/>
+      <c r="Q47" s="25"/>
+      <c r="R47" s="25"/>
+      <c r="S47" s="25"/>
+      <c r="T47" s="25"/>
+      <c r="U47" s="25"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>10</v>
       </c>
@@ -6190,56 +6255,56 @@
       <c r="D48" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="F48" s="26" t="s">
+      <c r="F48" s="38" t="s">
         <v>708</v>
       </c>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="28"/>
-      <c r="O48" s="44" t="s">
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="38"/>
+      <c r="K48" s="38"/>
+      <c r="L48" s="38"/>
+      <c r="O48" s="25" t="s">
         <v>744</v>
       </c>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
-      <c r="R48" s="44"/>
-      <c r="S48" s="44"/>
-      <c r="T48" s="44"/>
-      <c r="U48" s="44"/>
-    </row>
-    <row r="49" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P48" s="25"/>
+      <c r="Q48" s="25"/>
+      <c r="R48" s="25"/>
+      <c r="S48" s="25"/>
+      <c r="T48" s="25"/>
+      <c r="U48" s="25"/>
+    </row>
+    <row r="49" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>11</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="11" t="s">
+      <c r="B49" s="10"/>
+      <c r="C49" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="F49" s="26" t="s">
+      <c r="F49" s="38" t="s">
         <v>709</v>
       </c>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="28"/>
-      <c r="O49" s="44" t="s">
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="38"/>
+      <c r="K49" s="38"/>
+      <c r="L49" s="38"/>
+      <c r="O49" s="25" t="s">
         <v>745</v>
       </c>
-      <c r="P49" s="44"/>
-      <c r="Q49" s="44"/>
-      <c r="R49" s="44"/>
-      <c r="S49" s="44"/>
-      <c r="T49" s="44"/>
-      <c r="U49" s="44"/>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P49" s="25"/>
+      <c r="Q49" s="25"/>
+      <c r="R49" s="25"/>
+      <c r="S49" s="25"/>
+      <c r="T49" s="25"/>
+      <c r="U49" s="25"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>12</v>
       </c>
@@ -6250,15 +6315,15 @@
       <c r="D50" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="F50" s="26"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
-      <c r="L50" s="28"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>13</v>
       </c>
@@ -6269,17 +6334,17 @@
       <c r="D51" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="39" t="s">
         <v>710</v>
       </c>
-      <c r="G51" s="29"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="31"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>14</v>
       </c>
@@ -6290,26 +6355,26 @@
       <c r="D52" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="F52" s="26" t="s">
+      <c r="F52" s="38" t="s">
         <v>711</v>
       </c>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="28"/>
-      <c r="O52" s="44" t="s">
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="38"/>
+      <c r="L52" s="38"/>
+      <c r="O52" s="25" t="s">
         <v>751</v>
       </c>
-      <c r="P52" s="44"/>
-      <c r="Q52" s="44"/>
-      <c r="R52" s="44"/>
-      <c r="S52" s="44"/>
-      <c r="T52" s="44"/>
-      <c r="U52" s="44"/>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P52" s="25"/>
+      <c r="Q52" s="25"/>
+      <c r="R52" s="25"/>
+      <c r="S52" s="25"/>
+      <c r="T52" s="25"/>
+      <c r="U52" s="25"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>15</v>
       </c>
@@ -6320,26 +6385,26 @@
       <c r="D53" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="F53" s="26" t="s">
+      <c r="F53" s="38" t="s">
         <v>712</v>
       </c>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="28"/>
-      <c r="O53" s="44" t="s">
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="O53" s="25" t="s">
         <v>752</v>
       </c>
-      <c r="P53" s="44"/>
-      <c r="Q53" s="44"/>
-      <c r="R53" s="44"/>
-      <c r="S53" s="44"/>
-      <c r="T53" s="44"/>
-      <c r="U53" s="44"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P53" s="25"/>
+      <c r="Q53" s="25"/>
+      <c r="R53" s="25"/>
+      <c r="S53" s="25"/>
+      <c r="T53" s="25"/>
+      <c r="U53" s="25"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>16</v>
       </c>
@@ -6350,26 +6415,26 @@
       <c r="D54" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="F54" s="26" t="s">
+      <c r="F54" s="38" t="s">
         <v>713</v>
       </c>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-      <c r="L54" s="28"/>
-      <c r="O54" s="44" t="s">
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="O54" s="25" t="s">
         <v>753</v>
       </c>
-      <c r="P54" s="44"/>
-      <c r="Q54" s="44"/>
-      <c r="R54" s="44"/>
-      <c r="S54" s="44"/>
-      <c r="T54" s="44"/>
-      <c r="U54" s="44"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P54" s="25"/>
+      <c r="Q54" s="25"/>
+      <c r="R54" s="25"/>
+      <c r="S54" s="25"/>
+      <c r="T54" s="25"/>
+      <c r="U54" s="25"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>17</v>
       </c>
@@ -6380,26 +6445,26 @@
       <c r="D55" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="F55" s="26" t="s">
+      <c r="F55" s="38" t="s">
         <v>714</v>
       </c>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="28"/>
-      <c r="O55" s="44" t="s">
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+      <c r="O55" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P55" s="44"/>
-      <c r="Q55" s="44"/>
-      <c r="R55" s="44"/>
-      <c r="S55" s="44"/>
-      <c r="T55" s="44"/>
-      <c r="U55" s="44"/>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P55" s="25"/>
+      <c r="Q55" s="25"/>
+      <c r="R55" s="25"/>
+      <c r="S55" s="25"/>
+      <c r="T55" s="25"/>
+      <c r="U55" s="25"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>18</v>
       </c>
@@ -6410,26 +6475,26 @@
       <c r="D56" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="F56" s="26" t="s">
+      <c r="F56" s="38" t="s">
         <v>715</v>
       </c>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
-      <c r="L56" s="28"/>
-      <c r="O56" s="44" t="s">
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="38"/>
+      <c r="O56" s="25" t="s">
         <v>754</v>
       </c>
-      <c r="P56" s="44"/>
-      <c r="Q56" s="44"/>
-      <c r="R56" s="44"/>
-      <c r="S56" s="44"/>
-      <c r="T56" s="44"/>
-      <c r="U56" s="44"/>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P56" s="25"/>
+      <c r="Q56" s="25"/>
+      <c r="R56" s="25"/>
+      <c r="S56" s="25"/>
+      <c r="T56" s="25"/>
+      <c r="U56" s="25"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>19</v>
       </c>
@@ -6440,17 +6505,17 @@
       <c r="D57" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="O57" s="44" t="s">
+      <c r="O57" s="25" t="s">
         <v>755</v>
       </c>
-      <c r="P57" s="44"/>
-      <c r="Q57" s="44"/>
-      <c r="R57" s="44"/>
-      <c r="S57" s="44"/>
-      <c r="T57" s="44"/>
-      <c r="U57" s="44"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P57" s="25"/>
+      <c r="Q57" s="25"/>
+      <c r="R57" s="25"/>
+      <c r="S57" s="25"/>
+      <c r="T57" s="25"/>
+      <c r="U57" s="25"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>20</v>
       </c>
@@ -6469,7 +6534,7 @@
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>21</v>
       </c>
@@ -6480,17 +6545,17 @@
       <c r="D59" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="O59" s="44" t="s">
+      <c r="O59" s="25" t="s">
         <v>756</v>
       </c>
-      <c r="P59" s="44"/>
-      <c r="Q59" s="44"/>
-      <c r="R59" s="44"/>
-      <c r="S59" s="44"/>
-      <c r="T59" s="44"/>
-      <c r="U59" s="44"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P59" s="25"/>
+      <c r="Q59" s="25"/>
+      <c r="R59" s="25"/>
+      <c r="S59" s="25"/>
+      <c r="T59" s="25"/>
+      <c r="U59" s="25"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>22</v>
       </c>
@@ -6501,17 +6566,17 @@
       <c r="D60" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="O60" s="44" t="s">
+      <c r="O60" s="25" t="s">
         <v>757</v>
       </c>
-      <c r="P60" s="44"/>
-      <c r="Q60" s="44"/>
-      <c r="R60" s="44"/>
-      <c r="S60" s="44"/>
-      <c r="T60" s="44"/>
-      <c r="U60" s="44"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P60" s="25"/>
+      <c r="Q60" s="25"/>
+      <c r="R60" s="25"/>
+      <c r="S60" s="25"/>
+      <c r="T60" s="25"/>
+      <c r="U60" s="25"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>23</v>
       </c>
@@ -6522,85 +6587,85 @@
       <c r="D61" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="O61" s="44" t="s">
+      <c r="O61" s="25" t="s">
         <v>758</v>
       </c>
-      <c r="P61" s="44"/>
-      <c r="Q61" s="44"/>
-      <c r="R61" s="44"/>
-      <c r="S61" s="44"/>
-      <c r="T61" s="44"/>
-      <c r="U61" s="44"/>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="25"/>
+      <c r="S61" s="25"/>
+      <c r="T61" s="25"/>
+      <c r="U61" s="25"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>24</v>
       </c>
       <c r="B62" s="2"/>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>590</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="O62" s="44" t="s">
+      <c r="O62" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P62" s="44"/>
-      <c r="Q62" s="44"/>
-      <c r="R62" s="44"/>
-      <c r="S62" s="44"/>
-      <c r="T62" s="44"/>
-      <c r="U62" s="44"/>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P62" s="25"/>
+      <c r="Q62" s="25"/>
+      <c r="R62" s="25"/>
+      <c r="S62" s="25"/>
+      <c r="T62" s="25"/>
+      <c r="U62" s="25"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>25</v>
       </c>
       <c r="B63" s="2"/>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="O63" s="44" t="s">
+      <c r="O63" s="25" t="s">
         <v>759</v>
       </c>
-      <c r="P63" s="44"/>
-      <c r="Q63" s="44"/>
-      <c r="R63" s="44"/>
-      <c r="S63" s="44"/>
-      <c r="T63" s="44"/>
-      <c r="U63" s="44"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P63" s="25"/>
+      <c r="Q63" s="25"/>
+      <c r="R63" s="25"/>
+      <c r="S63" s="25"/>
+      <c r="T63" s="25"/>
+      <c r="U63" s="25"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>26</v>
       </c>
       <c r="B64" s="2"/>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>592</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="O64" s="44" t="s">
+      <c r="O64" s="25" t="s">
         <v>760</v>
       </c>
-      <c r="P64" s="44"/>
-      <c r="Q64" s="44"/>
-      <c r="R64" s="44"/>
-      <c r="S64" s="44"/>
-      <c r="T64" s="44"/>
-      <c r="U64" s="44"/>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P64" s="25"/>
+      <c r="Q64" s="25"/>
+      <c r="R64" s="25"/>
+      <c r="S64" s="25"/>
+      <c r="T64" s="25"/>
+      <c r="U64" s="25"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>27</v>
       </c>
       <c r="B65" s="2"/>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>593</v>
       </c>
       <c r="D65" s="2" t="s">
@@ -6614,93 +6679,93 @@
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>28</v>
       </c>
       <c r="B66" s="2"/>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>594</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="O66" s="44" t="s">
+      <c r="O66" s="25" t="s">
         <v>761</v>
       </c>
-      <c r="P66" s="44"/>
-      <c r="Q66" s="44"/>
-      <c r="R66" s="44"/>
-      <c r="S66" s="44"/>
-      <c r="T66" s="44"/>
-      <c r="U66" s="44"/>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="O67" s="44" t="s">
+      <c r="P66" s="25"/>
+      <c r="Q66" s="25"/>
+      <c r="R66" s="25"/>
+      <c r="S66" s="25"/>
+      <c r="T66" s="25"/>
+      <c r="U66" s="25"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O67" s="25" t="s">
         <v>762</v>
       </c>
-      <c r="P67" s="44"/>
-      <c r="Q67" s="44"/>
-      <c r="R67" s="44"/>
-      <c r="S67" s="44"/>
-      <c r="T67" s="44"/>
-      <c r="U67" s="44"/>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="O68" s="44" t="s">
+      <c r="P67" s="25"/>
+      <c r="Q67" s="25"/>
+      <c r="R67" s="25"/>
+      <c r="S67" s="25"/>
+      <c r="T67" s="25"/>
+      <c r="U67" s="25"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O68" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="P68" s="44"/>
-      <c r="Q68" s="44"/>
-      <c r="R68" s="44"/>
-      <c r="S68" s="44"/>
-      <c r="T68" s="44"/>
-      <c r="U68" s="44"/>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A69" s="35" t="s">
+      <c r="P68" s="25"/>
+      <c r="Q68" s="25"/>
+      <c r="R68" s="25"/>
+      <c r="S68" s="25"/>
+      <c r="T68" s="25"/>
+      <c r="U68" s="25"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69" s="24" t="s">
         <v>623</v>
       </c>
-      <c r="B69" s="35"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="O69" s="44" t="s">
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="O69" s="25" t="s">
         <v>763</v>
       </c>
-      <c r="P69" s="44"/>
-      <c r="Q69" s="44"/>
-      <c r="R69" s="44"/>
-      <c r="S69" s="44"/>
-      <c r="T69" s="44"/>
-      <c r="U69" s="44"/>
-    </row>
-    <row r="70" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P69" s="25"/>
+      <c r="Q69" s="25"/>
+      <c r="R69" s="25"/>
+      <c r="S69" s="25"/>
+      <c r="T69" s="25"/>
+      <c r="U69" s="25"/>
+    </row>
+    <row r="70" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>1</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10" t="s">
+      <c r="C70" s="7"/>
+      <c r="D70" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="O70" s="44" t="s">
+      <c r="O70" s="25" t="s">
         <v>764</v>
       </c>
-      <c r="P70" s="44"/>
-      <c r="Q70" s="44"/>
-      <c r="R70" s="44"/>
-      <c r="S70" s="44"/>
-      <c r="T70" s="44"/>
-      <c r="U70" s="44"/>
-    </row>
-    <row r="71" spans="1:21" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="P70" s="25"/>
+      <c r="Q70" s="25"/>
+      <c r="R70" s="25"/>
+      <c r="S70" s="25"/>
+      <c r="T70" s="25"/>
+      <c r="U70" s="25"/>
+    </row>
+    <row r="71" spans="1:21" ht="20" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
-      <c r="B71" s="36" t="s">
+      <c r="B71" s="27" t="s">
         <v>624</v>
       </c>
-      <c r="C71" s="37"/>
+      <c r="C71" s="28"/>
       <c r="D71" s="2" t="s">
         <v>644</v>
       </c>
@@ -6712,61 +6777,61 @@
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
     </row>
-    <row r="72" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>2</v>
       </c>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10" t="s">
+      <c r="B72" s="7"/>
+      <c r="C72" s="7" t="s">
         <v>625</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="O72" s="44" t="s">
+      <c r="O72" s="25" t="s">
         <v>765</v>
       </c>
-      <c r="P72" s="44"/>
-      <c r="Q72" s="44"/>
-      <c r="R72" s="44"/>
-      <c r="S72" s="44"/>
-      <c r="T72" s="44"/>
-      <c r="U72" s="44"/>
-    </row>
-    <row r="73" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P72" s="25"/>
+      <c r="Q72" s="25"/>
+      <c r="R72" s="25"/>
+      <c r="S72" s="25"/>
+      <c r="T72" s="25"/>
+      <c r="U72" s="25"/>
+    </row>
+    <row r="73" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>3</v>
       </c>
       <c r="B73" s="2"/>
-      <c r="C73" s="10" t="s">
+      <c r="C73" s="7" t="s">
         <v>626</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="O73" s="44" t="s">
+      <c r="O73" s="25" t="s">
         <v>766</v>
       </c>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
-      <c r="R73" s="44"/>
-      <c r="S73" s="44"/>
-      <c r="T73" s="44"/>
-      <c r="U73" s="44"/>
-    </row>
-    <row r="74" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P73" s="25"/>
+      <c r="Q73" s="25"/>
+      <c r="R73" s="25"/>
+      <c r="S73" s="25"/>
+      <c r="T73" s="25"/>
+      <c r="U73" s="25"/>
+    </row>
+    <row r="74" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>4</v>
       </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10" t="s">
+      <c r="B74" s="7"/>
+      <c r="C74" s="7" t="s">
         <v>627</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>5</v>
       </c>
@@ -6778,7 +6843,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>6</v>
       </c>
@@ -6789,17 +6854,17 @@
       <c r="D76" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="O76" s="26" t="s">
+      <c r="O76" s="19" t="s">
         <v>767</v>
       </c>
-      <c r="P76" s="27"/>
-      <c r="Q76" s="27"/>
-      <c r="R76" s="27"/>
-      <c r="S76" s="27"/>
-      <c r="T76" s="27"/>
-      <c r="U76" s="28"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P76" s="20"/>
+      <c r="Q76" s="20"/>
+      <c r="R76" s="20"/>
+      <c r="S76" s="20"/>
+      <c r="T76" s="20"/>
+      <c r="U76" s="21"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>7</v>
       </c>
@@ -6810,17 +6875,17 @@
       <c r="D77" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="O77" s="26" t="s">
+      <c r="O77" s="19" t="s">
         <v>768</v>
       </c>
-      <c r="P77" s="27"/>
-      <c r="Q77" s="27"/>
-      <c r="R77" s="27"/>
-      <c r="S77" s="27"/>
-      <c r="T77" s="27"/>
-      <c r="U77" s="28"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
+      <c r="R77" s="20"/>
+      <c r="S77" s="20"/>
+      <c r="T77" s="20"/>
+      <c r="U77" s="21"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>8</v>
       </c>
@@ -6831,17 +6896,17 @@
       <c r="D78" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="O78" s="26" t="s">
+      <c r="O78" s="19" t="s">
         <v>769</v>
       </c>
-      <c r="P78" s="27"/>
-      <c r="Q78" s="27"/>
-      <c r="R78" s="27"/>
-      <c r="S78" s="27"/>
-      <c r="T78" s="27"/>
-      <c r="U78" s="28"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P78" s="20"/>
+      <c r="Q78" s="20"/>
+      <c r="R78" s="20"/>
+      <c r="S78" s="20"/>
+      <c r="T78" s="20"/>
+      <c r="U78" s="21"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>9</v>
       </c>
@@ -6852,38 +6917,38 @@
       <c r="D79" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="O79" s="26" t="s">
+      <c r="O79" s="19" t="s">
         <v>768</v>
       </c>
-      <c r="P79" s="27"/>
-      <c r="Q79" s="27"/>
-      <c r="R79" s="27"/>
-      <c r="S79" s="27"/>
-      <c r="T79" s="27"/>
-      <c r="U79" s="28"/>
-    </row>
-    <row r="80" spans="1:21" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="P79" s="20"/>
+      <c r="Q79" s="20"/>
+      <c r="R79" s="20"/>
+      <c r="S79" s="20"/>
+      <c r="T79" s="20"/>
+      <c r="U79" s="21"/>
+    </row>
+    <row r="80" spans="1:21" ht="20" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>10</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11" t="s">
+      <c r="C80" s="8"/>
+      <c r="D80" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="O80" s="26" t="s">
+      <c r="O80" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="P80" s="27"/>
-      <c r="Q80" s="27"/>
-      <c r="R80" s="27"/>
-      <c r="S80" s="27"/>
-      <c r="T80" s="27"/>
-      <c r="U80" s="28"/>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P80" s="20"/>
+      <c r="Q80" s="20"/>
+      <c r="R80" s="20"/>
+      <c r="S80" s="20"/>
+      <c r="T80" s="20"/>
+      <c r="U80" s="21"/>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>11</v>
       </c>
@@ -6894,17 +6959,17 @@
       <c r="D81" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="O81" s="26" t="s">
+      <c r="O81" s="19" t="s">
         <v>771</v>
       </c>
-      <c r="P81" s="27"/>
-      <c r="Q81" s="27"/>
-      <c r="R81" s="27"/>
-      <c r="S81" s="27"/>
-      <c r="T81" s="27"/>
-      <c r="U81" s="28"/>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="20"/>
+      <c r="U81" s="21"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>12</v>
       </c>
@@ -6915,17 +6980,17 @@
       <c r="D82" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="O82" s="26" t="s">
+      <c r="O82" s="19" t="s">
         <v>770</v>
       </c>
-      <c r="P82" s="27"/>
-      <c r="Q82" s="27"/>
-      <c r="R82" s="27"/>
-      <c r="S82" s="27"/>
-      <c r="T82" s="27"/>
-      <c r="U82" s="28"/>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P82" s="20"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="21"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>13</v>
       </c>
@@ -6944,7 +7009,7 @@
       <c r="T83" s="2"/>
       <c r="U83" s="2"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>14</v>
       </c>
@@ -6955,17 +7020,17 @@
       <c r="D84" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="O84" s="26" t="s">
+      <c r="O84" s="19" t="s">
         <v>772</v>
       </c>
-      <c r="P84" s="27"/>
-      <c r="Q84" s="27"/>
-      <c r="R84" s="27"/>
-      <c r="S84" s="27"/>
-      <c r="T84" s="27"/>
-      <c r="U84" s="28"/>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P84" s="20"/>
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="20"/>
+      <c r="U84" s="21"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>15</v>
       </c>
@@ -6976,17 +7041,17 @@
       <c r="D85" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="O85" s="26" t="s">
+      <c r="O85" s="19" t="s">
         <v>773</v>
       </c>
-      <c r="P85" s="27"/>
-      <c r="Q85" s="27"/>
-      <c r="R85" s="27"/>
-      <c r="S85" s="27"/>
-      <c r="T85" s="27"/>
-      <c r="U85" s="28"/>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P85" s="20"/>
+      <c r="Q85" s="20"/>
+      <c r="R85" s="20"/>
+      <c r="S85" s="20"/>
+      <c r="T85" s="20"/>
+      <c r="U85" s="21"/>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>16</v>
       </c>
@@ -6997,17 +7062,17 @@
       <c r="D86" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="O86" s="26" t="s">
+      <c r="O86" s="19" t="s">
         <v>774</v>
       </c>
-      <c r="P86" s="27"/>
-      <c r="Q86" s="27"/>
-      <c r="R86" s="27"/>
-      <c r="S86" s="27"/>
-      <c r="T86" s="27"/>
-      <c r="U86" s="28"/>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P86" s="20"/>
+      <c r="Q86" s="20"/>
+      <c r="R86" s="20"/>
+      <c r="S86" s="20"/>
+      <c r="T86" s="20"/>
+      <c r="U86" s="21"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>17</v>
       </c>
@@ -7020,17 +7085,17 @@
       <c r="D87" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="O87" s="26" t="s">
+      <c r="O87" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="P87" s="27"/>
-      <c r="Q87" s="27"/>
-      <c r="R87" s="27"/>
-      <c r="S87" s="27"/>
-      <c r="T87" s="27"/>
-      <c r="U87" s="28"/>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P87" s="20"/>
+      <c r="Q87" s="20"/>
+      <c r="R87" s="20"/>
+      <c r="S87" s="20"/>
+      <c r="T87" s="20"/>
+      <c r="U87" s="21"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>18</v>
       </c>
@@ -7041,17 +7106,17 @@
       <c r="D88" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="O88" s="26" t="s">
+      <c r="O88" s="19" t="s">
         <v>776</v>
       </c>
-      <c r="P88" s="27"/>
-      <c r="Q88" s="27"/>
-      <c r="R88" s="27"/>
-      <c r="S88" s="27"/>
-      <c r="T88" s="27"/>
-      <c r="U88" s="28"/>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P88" s="20"/>
+      <c r="Q88" s="20"/>
+      <c r="R88" s="20"/>
+      <c r="S88" s="20"/>
+      <c r="T88" s="20"/>
+      <c r="U88" s="21"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>19</v>
       </c>
@@ -7062,17 +7127,17 @@
       <c r="D89" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="O89" s="26" t="s">
+      <c r="O89" s="19" t="s">
         <v>775</v>
       </c>
-      <c r="P89" s="27"/>
-      <c r="Q89" s="27"/>
-      <c r="R89" s="27"/>
-      <c r="S89" s="27"/>
-      <c r="T89" s="27"/>
-      <c r="U89" s="28"/>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P89" s="20"/>
+      <c r="Q89" s="20"/>
+      <c r="R89" s="20"/>
+      <c r="S89" s="20"/>
+      <c r="T89" s="20"/>
+      <c r="U89" s="21"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>20</v>
       </c>
@@ -7091,7 +7156,7 @@
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>21</v>
       </c>
@@ -7102,17 +7167,17 @@
       <c r="D91" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="O91" s="26" t="s">
+      <c r="O91" s="19" t="s">
         <v>777</v>
       </c>
-      <c r="P91" s="27"/>
-      <c r="Q91" s="27"/>
-      <c r="R91" s="27"/>
-      <c r="S91" s="27"/>
-      <c r="T91" s="27"/>
-      <c r="U91" s="28"/>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P91" s="20"/>
+      <c r="Q91" s="20"/>
+      <c r="R91" s="20"/>
+      <c r="S91" s="20"/>
+      <c r="T91" s="20"/>
+      <c r="U91" s="21"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>22</v>
       </c>
@@ -7133,212 +7198,161 @@
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>23</v>
       </c>
       <c r="B93" s="2"/>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>642</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="O93" s="26" t="s">
+      <c r="O93" s="19" t="s">
         <v>779</v>
       </c>
-      <c r="P93" s="27"/>
-      <c r="Q93" s="27"/>
-      <c r="R93" s="27"/>
-      <c r="S93" s="27"/>
-      <c r="T93" s="27"/>
-      <c r="U93" s="28"/>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="O94" s="26" t="s">
+      <c r="P93" s="20"/>
+      <c r="Q93" s="20"/>
+      <c r="R93" s="20"/>
+      <c r="S93" s="20"/>
+      <c r="T93" s="20"/>
+      <c r="U93" s="21"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O94" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="P94" s="27"/>
-      <c r="Q94" s="27"/>
-      <c r="R94" s="27"/>
-      <c r="S94" s="27"/>
-      <c r="T94" s="27"/>
-      <c r="U94" s="28"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="O95" s="26" t="s">
+      <c r="P94" s="20"/>
+      <c r="Q94" s="20"/>
+      <c r="R94" s="20"/>
+      <c r="S94" s="20"/>
+      <c r="T94" s="20"/>
+      <c r="U94" s="21"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O95" s="19" t="s">
         <v>780</v>
       </c>
-      <c r="P95" s="27"/>
-      <c r="Q95" s="27"/>
-      <c r="R95" s="27"/>
-      <c r="S95" s="27"/>
-      <c r="T95" s="27"/>
-      <c r="U95" s="28"/>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="O96" s="26" t="s">
+      <c r="P95" s="20"/>
+      <c r="Q95" s="20"/>
+      <c r="R95" s="20"/>
+      <c r="S95" s="20"/>
+      <c r="T95" s="20"/>
+      <c r="U95" s="21"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O96" s="19" t="s">
         <v>781</v>
       </c>
-      <c r="P96" s="27"/>
-      <c r="Q96" s="27"/>
-      <c r="R96" s="27"/>
-      <c r="S96" s="27"/>
-      <c r="T96" s="27"/>
-      <c r="U96" s="28"/>
-    </row>
-    <row r="97" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O97" s="26" t="s">
+      <c r="P96" s="20"/>
+      <c r="Q96" s="20"/>
+      <c r="R96" s="20"/>
+      <c r="S96" s="20"/>
+      <c r="T96" s="20"/>
+      <c r="U96" s="21"/>
+    </row>
+    <row r="97" spans="15:21" x14ac:dyDescent="0.25">
+      <c r="O97" s="19" t="s">
         <v>782</v>
       </c>
-      <c r="P97" s="27"/>
-      <c r="Q97" s="27"/>
-      <c r="R97" s="27"/>
-      <c r="S97" s="27"/>
-      <c r="T97" s="27"/>
-      <c r="U97" s="28"/>
-    </row>
-    <row r="98" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O98" s="44" t="s">
+      <c r="P97" s="20"/>
+      <c r="Q97" s="20"/>
+      <c r="R97" s="20"/>
+      <c r="S97" s="20"/>
+      <c r="T97" s="20"/>
+      <c r="U97" s="21"/>
+    </row>
+    <row r="98" spans="15:21" x14ac:dyDescent="0.25">
+      <c r="O98" s="25" t="s">
         <v>783</v>
       </c>
-      <c r="P98" s="44"/>
-      <c r="Q98" s="44"/>
-      <c r="R98" s="44"/>
-      <c r="S98" s="44" t="s">
+      <c r="P98" s="25"/>
+      <c r="Q98" s="25"/>
+      <c r="R98" s="25"/>
+      <c r="S98" s="25" t="s">
         <v>784</v>
       </c>
-      <c r="T98" s="44"/>
-      <c r="U98" s="44"/>
-    </row>
-    <row r="99" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O99" s="44" t="s">
+      <c r="T98" s="25"/>
+      <c r="U98" s="25"/>
+    </row>
+    <row r="99" spans="15:21" x14ac:dyDescent="0.25">
+      <c r="O99" s="25" t="s">
         <v>785</v>
       </c>
-      <c r="P99" s="44"/>
-      <c r="Q99" s="44"/>
-      <c r="R99" s="44"/>
-      <c r="S99" s="44" t="s">
+      <c r="P99" s="25"/>
+      <c r="Q99" s="25"/>
+      <c r="R99" s="25"/>
+      <c r="S99" s="25" t="s">
         <v>788</v>
       </c>
-      <c r="T99" s="44"/>
-      <c r="U99" s="44"/>
-    </row>
-    <row r="100" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O100" s="44" t="s">
+      <c r="T99" s="25"/>
+      <c r="U99" s="25"/>
+    </row>
+    <row r="100" spans="15:21" x14ac:dyDescent="0.25">
+      <c r="O100" s="25" t="s">
         <v>786</v>
       </c>
-      <c r="P100" s="44"/>
-      <c r="Q100" s="44"/>
-      <c r="R100" s="44"/>
-      <c r="S100" s="44" t="s">
+      <c r="P100" s="25"/>
+      <c r="Q100" s="25"/>
+      <c r="R100" s="25"/>
+      <c r="S100" s="25" t="s">
         <v>789</v>
       </c>
-      <c r="T100" s="44"/>
-      <c r="U100" s="44"/>
-    </row>
-    <row r="101" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O101" s="44" t="s">
+      <c r="T100" s="25"/>
+      <c r="U100" s="25"/>
+    </row>
+    <row r="101" spans="15:21" x14ac:dyDescent="0.25">
+      <c r="O101" s="25" t="s">
         <v>787</v>
       </c>
-      <c r="P101" s="44"/>
-      <c r="Q101" s="44"/>
-      <c r="R101" s="44"/>
-      <c r="S101" s="44" t="s">
+      <c r="P101" s="25"/>
+      <c r="Q101" s="25"/>
+      <c r="R101" s="25"/>
+      <c r="S101" s="25" t="s">
         <v>790</v>
       </c>
-      <c r="T101" s="44"/>
-      <c r="U101" s="44"/>
+      <c r="T101" s="25"/>
+      <c r="U101" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="O95:U95"/>
-    <mergeCell ref="O96:U96"/>
-    <mergeCell ref="O97:U97"/>
-    <mergeCell ref="O88:U88"/>
-    <mergeCell ref="O89:U89"/>
-    <mergeCell ref="O91:U91"/>
-    <mergeCell ref="O93:U93"/>
-    <mergeCell ref="O94:U94"/>
-    <mergeCell ref="O100:R100"/>
-    <mergeCell ref="O101:R101"/>
-    <mergeCell ref="S99:U99"/>
-    <mergeCell ref="S100:U100"/>
-    <mergeCell ref="S101:U101"/>
-    <mergeCell ref="O73:U73"/>
-    <mergeCell ref="O98:R98"/>
-    <mergeCell ref="S98:U98"/>
-    <mergeCell ref="O99:R99"/>
-    <mergeCell ref="O76:U76"/>
-    <mergeCell ref="O77:U77"/>
-    <mergeCell ref="O78:U78"/>
-    <mergeCell ref="O79:U79"/>
-    <mergeCell ref="O80:U80"/>
-    <mergeCell ref="O81:U81"/>
-    <mergeCell ref="O82:U82"/>
-    <mergeCell ref="O84:U84"/>
-    <mergeCell ref="O85:U85"/>
-    <mergeCell ref="O86:U86"/>
-    <mergeCell ref="O87:U87"/>
-    <mergeCell ref="O67:U67"/>
-    <mergeCell ref="O68:U68"/>
-    <mergeCell ref="O69:U69"/>
-    <mergeCell ref="O70:U70"/>
-    <mergeCell ref="O72:U72"/>
-    <mergeCell ref="O61:U61"/>
-    <mergeCell ref="O62:U62"/>
-    <mergeCell ref="O63:U63"/>
-    <mergeCell ref="O64:U64"/>
-    <mergeCell ref="O66:U66"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="O60:U60"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="O52:U52"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="O43:U43"/>
-    <mergeCell ref="O44:U44"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="O46:U46"/>
-    <mergeCell ref="O47:U47"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="O39:U39"/>
-    <mergeCell ref="O40:U40"/>
-    <mergeCell ref="O41:U41"/>
-    <mergeCell ref="O31:U31"/>
-    <mergeCell ref="O32:U32"/>
-    <mergeCell ref="O33:U33"/>
-    <mergeCell ref="O35:U35"/>
-    <mergeCell ref="O36:U36"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="O28:U28"/>
-    <mergeCell ref="O29:U29"/>
-    <mergeCell ref="O30:U30"/>
-    <mergeCell ref="O2:U2"/>
-    <mergeCell ref="O12:U12"/>
-    <mergeCell ref="O13:U13"/>
-    <mergeCell ref="O11:U11"/>
-    <mergeCell ref="O14:U14"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="O3:U3"/>
-    <mergeCell ref="O4:U4"/>
-    <mergeCell ref="O5:U5"/>
-    <mergeCell ref="O6:U6"/>
-    <mergeCell ref="O7:U7"/>
-    <mergeCell ref="O8:U8"/>
-    <mergeCell ref="O10:U10"/>
-    <mergeCell ref="O15:U15"/>
-    <mergeCell ref="O17:U17"/>
-    <mergeCell ref="O18:U18"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="F56:L56"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="F48:L48"/>
+    <mergeCell ref="F49:L49"/>
+    <mergeCell ref="F50:L50"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="F52:L52"/>
+    <mergeCell ref="F53:L53"/>
+    <mergeCell ref="F54:L54"/>
+    <mergeCell ref="F55:L55"/>
+    <mergeCell ref="F45:L45"/>
+    <mergeCell ref="F46:L46"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="F18:L18"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="F22:L22"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="F25:L25"/>
+    <mergeCell ref="F28:L28"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="F37:L37"/>
+    <mergeCell ref="F32:L32"/>
+    <mergeCell ref="F43:L43"/>
+    <mergeCell ref="F35:L35"/>
+    <mergeCell ref="F26:L26"/>
+    <mergeCell ref="F27:L27"/>
+    <mergeCell ref="F44:L44"/>
+    <mergeCell ref="F41:L41"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="F36:L36"/>
+    <mergeCell ref="F38:L38"/>
+    <mergeCell ref="F40:L40"/>
+    <mergeCell ref="G39:L39"/>
     <mergeCell ref="A69:D69"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="F2:L2"/>
@@ -7363,42 +7377,93 @@
     <mergeCell ref="F19:L19"/>
     <mergeCell ref="F30:L30"/>
     <mergeCell ref="F31:L31"/>
-    <mergeCell ref="F35:L35"/>
-    <mergeCell ref="F26:L26"/>
-    <mergeCell ref="F27:L27"/>
-    <mergeCell ref="F44:L44"/>
-    <mergeCell ref="F41:L41"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="F36:L36"/>
-    <mergeCell ref="F38:L38"/>
-    <mergeCell ref="F40:L40"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="F45:L45"/>
-    <mergeCell ref="F46:L46"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="F8:L8"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="F18:L18"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="F22:L22"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="F25:L25"/>
-    <mergeCell ref="F28:L28"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="F37:L37"/>
-    <mergeCell ref="F32:L32"/>
-    <mergeCell ref="F43:L43"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="F48:L48"/>
-    <mergeCell ref="F49:L49"/>
-    <mergeCell ref="F50:L50"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="F52:L52"/>
-    <mergeCell ref="F53:L53"/>
-    <mergeCell ref="F54:L54"/>
-    <mergeCell ref="F55:L55"/>
-    <mergeCell ref="F56:L56"/>
+    <mergeCell ref="O2:U2"/>
+    <mergeCell ref="O12:U12"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="O11:U11"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="O3:U3"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="O7:U7"/>
+    <mergeCell ref="O8:U8"/>
+    <mergeCell ref="O10:U10"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="O17:U17"/>
+    <mergeCell ref="O18:U18"/>
+    <mergeCell ref="O19:U19"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="O32:U32"/>
+    <mergeCell ref="O33:U33"/>
+    <mergeCell ref="O35:U35"/>
+    <mergeCell ref="O36:U36"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="O28:U28"/>
+    <mergeCell ref="O29:U29"/>
+    <mergeCell ref="O30:U30"/>
+    <mergeCell ref="O43:U43"/>
+    <mergeCell ref="O44:U44"/>
+    <mergeCell ref="O45:U45"/>
+    <mergeCell ref="O46:U46"/>
+    <mergeCell ref="O47:U47"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="O39:U39"/>
+    <mergeCell ref="O40:U40"/>
+    <mergeCell ref="O41:U41"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="O60:U60"/>
+    <mergeCell ref="O48:U48"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="O52:U52"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="O67:U67"/>
+    <mergeCell ref="O68:U68"/>
+    <mergeCell ref="O69:U69"/>
+    <mergeCell ref="O70:U70"/>
+    <mergeCell ref="O72:U72"/>
+    <mergeCell ref="O61:U61"/>
+    <mergeCell ref="O62:U62"/>
+    <mergeCell ref="O63:U63"/>
+    <mergeCell ref="O64:U64"/>
+    <mergeCell ref="O66:U66"/>
+    <mergeCell ref="O101:R101"/>
+    <mergeCell ref="S99:U99"/>
+    <mergeCell ref="S100:U100"/>
+    <mergeCell ref="S101:U101"/>
+    <mergeCell ref="O73:U73"/>
+    <mergeCell ref="O98:R98"/>
+    <mergeCell ref="S98:U98"/>
+    <mergeCell ref="O99:R99"/>
+    <mergeCell ref="O76:U76"/>
+    <mergeCell ref="O77:U77"/>
+    <mergeCell ref="O78:U78"/>
+    <mergeCell ref="O79:U79"/>
+    <mergeCell ref="O80:U80"/>
+    <mergeCell ref="O81:U81"/>
+    <mergeCell ref="O82:U82"/>
+    <mergeCell ref="O84:U84"/>
+    <mergeCell ref="O85:U85"/>
+    <mergeCell ref="O86:U86"/>
+    <mergeCell ref="O87:U87"/>
+    <mergeCell ref="O95:U95"/>
+    <mergeCell ref="O96:U96"/>
+    <mergeCell ref="O97:U97"/>
+    <mergeCell ref="O88:U88"/>
+    <mergeCell ref="O89:U89"/>
+    <mergeCell ref="O91:U91"/>
+    <mergeCell ref="O93:U93"/>
+    <mergeCell ref="O94:U94"/>
+    <mergeCell ref="O100:R100"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7408,36 +7473,36 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF088B7-57DB-42FE-8A82-081056E8782F}">
   <dimension ref="A2:U82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="41" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="40"/>
-      <c r="F2" s="26" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34"/>
+      <c r="F2" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="28"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="21"/>
       <c r="N2" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -7461,7 +7526,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -7472,20 +7537,20 @@
       <c r="D4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="28"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
       <c r="N4" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -7496,20 +7561,20 @@
       <c r="D5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="19" t="s">
         <v>791</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="28"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
       <c r="N5" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -7520,17 +7585,17 @@
       <c r="D6" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="19" t="s">
         <v>792</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="28"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="21"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -7552,7 +7617,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -7563,7 +7628,7 @@
       <c r="D8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G8" s="29"/>
@@ -7576,7 +7641,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -7587,20 +7652,20 @@
       <c r="D9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="28"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21"/>
       <c r="N9" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -7611,20 +7676,20 @@
       <c r="D10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="28"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21"/>
       <c r="N10" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -7635,20 +7700,20 @@
       <c r="D11" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="28"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
       <c r="N11" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -7659,20 +7724,20 @@
       <c r="D12" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="35" t="s">
         <v>793</v>
       </c>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="43"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37"/>
       <c r="N12" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -7694,7 +7759,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -7707,7 +7772,7 @@
       <c r="D14" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G14" s="29"/>
@@ -7720,7 +7785,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -7733,20 +7798,20 @@
       <c r="D15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="28"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="21"/>
       <c r="N15" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -7759,20 +7824,20 @@
       <c r="D16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="28"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="21"/>
       <c r="N16" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -7796,7 +7861,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -7809,7 +7874,7 @@
       <c r="D18" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>199</v>
       </c>
       <c r="G18" s="2"/>
@@ -7822,7 +7887,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -7835,20 +7900,20 @@
       <c r="D19" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="21"/>
       <c r="N19" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -7861,20 +7926,20 @@
       <c r="D20" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="28"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="21"/>
       <c r="N20" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -7898,7 +7963,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -7911,7 +7976,7 @@
       <c r="D22" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G22" s="29"/>
@@ -7924,7 +7989,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>152</v>
@@ -7933,20 +7998,20 @@
       <c r="D23" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="28"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="21"/>
       <c r="N23" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -7970,7 +8035,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -7983,7 +8048,7 @@
       <c r="D25" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>204</v>
       </c>
       <c r="G25" s="2"/>
@@ -7993,7 +8058,7 @@
       <c r="K25" s="30"/>
       <c r="L25" s="31"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -8006,20 +8071,20 @@
       <c r="D26" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="28"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="21"/>
       <c r="N26" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -8043,7 +8108,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -8054,7 +8119,7 @@
       <c r="D28" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G28" s="2"/>
@@ -8067,7 +8132,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -8075,23 +8140,23 @@
         <v>162</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="28"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="21"/>
       <c r="N29" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -8099,29 +8164,29 @@
         <v>163</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="28"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="21"/>
       <c r="N30" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>126</v>
       </c>
       <c r="F31" s="29"/>
@@ -8135,7 +8200,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -8143,10 +8208,10 @@
         <v>165</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="3" t="s">
         <v>208</v>
       </c>
       <c r="G32" s="29"/>
@@ -8159,7 +8224,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -8167,42 +8232,42 @@
         <v>166</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="28"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="19" t="s">
         <v>794</v>
       </c>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="28"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="21"/>
       <c r="N34" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>30</v>
       </c>
@@ -8210,7 +8275,7 @@
       <c r="C35" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F35" s="29"/>
@@ -8224,18 +8289,18 @@
         <v>246</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>31</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G36" s="29"/>
@@ -8248,7 +8313,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>32</v>
       </c>
@@ -8256,37 +8321,37 @@
         <v>170</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="28"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="21"/>
       <c r="N37" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F38" s="26" t="s">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F38" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="21"/>
       <c r="N38" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F39" s="29"/>
       <c r="G39" s="30"/>
       <c r="H39" s="30"/>
@@ -8298,24 +8363,24 @@
         <v>249</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="38" t="s">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="39"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="40"/>
-      <c r="F40" s="44" t="s">
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="34"/>
+      <c r="F40" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
       <c r="I40" s="30"/>
       <c r="J40" s="30"/>
       <c r="K40" s="30"/>
       <c r="L40" s="31"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>1</v>
       </c>
@@ -8326,20 +8391,20 @@
       <c r="D41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F41" s="26" t="s">
+      <c r="F41" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="28"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="21"/>
       <c r="N41" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2</v>
       </c>
@@ -8350,20 +8415,20 @@
       <c r="D42" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="28"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="21"/>
       <c r="N42" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>3</v>
       </c>
@@ -8376,20 +8441,20 @@
       <c r="D43" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="28"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="21"/>
       <c r="N43" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>4</v>
       </c>
@@ -8400,20 +8465,20 @@
       <c r="D44" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="26" t="s">
+      <c r="F44" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="28"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="21"/>
       <c r="N44" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>5</v>
       </c>
@@ -8424,20 +8489,20 @@
       <c r="D45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F45" s="26" t="s">
+      <c r="F45" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="28"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="21"/>
       <c r="N45" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>6</v>
       </c>
@@ -8448,20 +8513,20 @@
       <c r="D46" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F46" s="26" t="s">
+      <c r="F46" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="28"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="21"/>
       <c r="N46" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>7</v>
@@ -8474,7 +8539,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>7</v>
       </c>
@@ -8486,7 +8551,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
         <v>34</v>
@@ -8499,7 +8564,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>8</v>
       </c>
@@ -8512,15 +8577,15 @@
       <c r="D50" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N50" s="5" t="s">
+      <c r="N50" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>9</v>
       </c>
@@ -8537,7 +8602,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>10</v>
       </c>
@@ -8554,7 +8619,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -8564,7 +8629,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>11</v>
       </c>
@@ -8581,7 +8646,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>12</v>
       </c>
@@ -8596,7 +8661,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
         <v>19</v>
@@ -8609,7 +8674,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>13</v>
       </c>
@@ -8626,7 +8691,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>14</v>
       </c>
@@ -8641,7 +8706,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>15</v>
       </c>
@@ -8656,7 +8721,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>16</v>
       </c>
@@ -8670,30 +8735,30 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N62" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A63" s="35" t="s">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="N63" s="6" t="s">
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="N63" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
-      <c r="T63" s="6"/>
-      <c r="U63" s="6"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+      <c r="S63" s="5"/>
+      <c r="T63" s="5"/>
+      <c r="U63" s="5"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>1</v>
       </c>
@@ -8706,18 +8771,11 @@
       <c r="D64" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N64" s="7" t="s">
+      <c r="N64" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="O64" s="7"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="7"/>
-      <c r="T64" s="7"/>
-      <c r="U64" s="7"/>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>2</v>
       </c>
@@ -8728,18 +8786,18 @@
       <c r="D65" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="N65" s="6" t="s">
+      <c r="N65" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
-      <c r="R65" s="6"/>
-      <c r="S65" s="6"/>
-      <c r="T65" s="6"/>
-      <c r="U65" s="6"/>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5"/>
+      <c r="S65" s="5"/>
+      <c r="T65" s="5"/>
+      <c r="U65" s="5"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>50</v>
@@ -8750,16 +8808,8 @@
       <c r="D66" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N66" s="7"/>
-      <c r="O66" s="7"/>
-      <c r="P66" s="7"/>
-      <c r="Q66" s="7"/>
-      <c r="R66" s="7"/>
-      <c r="S66" s="7"/>
-      <c r="T66" s="7"/>
-      <c r="U66" s="7"/>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>3</v>
       </c>
@@ -8772,18 +8822,17 @@
       <c r="D67" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="N67" s="6" t="s">
+      <c r="N67" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="O67" s="6"/>
-      <c r="P67" s="6"/>
-      <c r="Q67" s="6"/>
-      <c r="R67" s="6"/>
-      <c r="S67" s="6"/>
-      <c r="T67" s="6"/>
-      <c r="U67" s="7"/>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5"/>
+      <c r="S67" s="5"/>
+      <c r="T67" s="5"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>4</v>
       </c>
@@ -8796,18 +8845,11 @@
       <c r="D68" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N68" s="8" t="s">
+      <c r="N68" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
-      <c r="Q68" s="7"/>
-      <c r="R68" s="7"/>
-      <c r="S68" s="7"/>
-      <c r="T68" s="7"/>
-      <c r="U68" s="7"/>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>5</v>
       </c>
@@ -8818,18 +8860,11 @@
       <c r="D69" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N69" s="7" t="s">
+      <c r="N69" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="O69" s="7"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="7"/>
-      <c r="T69" s="7"/>
-      <c r="U69" s="8"/>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>6</v>
       </c>
@@ -8840,16 +8875,8 @@
       <c r="D70" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="7"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="7"/>
-      <c r="T70" s="7"/>
-      <c r="U70" s="7"/>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>7</v>
       </c>
@@ -8862,18 +8889,11 @@
       <c r="D71" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N71" s="7" t="s">
+      <c r="N71" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="O71" s="7"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="7"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="7"/>
-      <c r="T71" s="7"/>
-      <c r="U71" s="7"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>8</v>
       </c>
@@ -8886,18 +8906,11 @@
       <c r="D72" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N72" s="8" t="s">
+      <c r="N72" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="O72" s="7"/>
-      <c r="P72" s="7"/>
-      <c r="Q72" s="7"/>
-      <c r="R72" s="7"/>
-      <c r="S72" s="7"/>
-      <c r="T72" s="7"/>
-      <c r="U72" s="7"/>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>9</v>
       </c>
@@ -8910,18 +8923,11 @@
       <c r="D73" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N73" s="7" t="s">
+      <c r="N73" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="O73" s="7"/>
-      <c r="P73" s="7"/>
-      <c r="Q73" s="7"/>
-      <c r="R73" s="7"/>
-      <c r="S73" s="7"/>
-      <c r="T73" s="7"/>
-      <c r="U73" s="7"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>10</v>
       </c>
@@ -8934,16 +8940,8 @@
       <c r="D74" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="7"/>
-      <c r="S74" s="7"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="7"/>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>11</v>
       </c>
@@ -8956,18 +8954,18 @@
       <c r="D75" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N75" s="6" t="s">
+      <c r="N75" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="O75" s="6"/>
-      <c r="P75" s="6"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="6"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="5"/>
+      <c r="R75" s="5"/>
+      <c r="S75" s="5"/>
+      <c r="T75" s="5"/>
+      <c r="U75" s="5"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>12</v>
       </c>
@@ -8980,18 +8978,18 @@
       <c r="D76" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="N76" s="6" t="s">
+      <c r="N76" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="O76" s="6"/>
-      <c r="P76" s="6"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="5"/>
+      <c r="R76" s="5"/>
+      <c r="S76" s="5"/>
+      <c r="T76" s="5"/>
+      <c r="U76" s="5"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>13</v>
       </c>
@@ -9002,112 +9000,72 @@
       <c r="D77" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N77" s="6" t="s">
+      <c r="N77" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="O77" s="6"/>
-      <c r="P77" s="6"/>
-      <c r="Q77" s="6"/>
-      <c r="R77" s="6"/>
-      <c r="S77" s="6"/>
-      <c r="T77" s="6"/>
-      <c r="U77" s="6"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="N78" s="8" t="s">
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="5"/>
+      <c r="R77" s="5"/>
+      <c r="S77" s="5"/>
+      <c r="T77" s="5"/>
+      <c r="U77" s="5"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N78" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="O78" s="7"/>
-      <c r="P78" s="7"/>
-      <c r="Q78" s="7"/>
-      <c r="R78" s="7"/>
-      <c r="S78" s="7"/>
-      <c r="T78" s="7"/>
-      <c r="U78" s="7"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="N79" s="9" t="s">
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N79" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="O79" s="9"/>
-      <c r="P79" s="9"/>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="N80" s="6" t="s">
+      <c r="O79" s="6"/>
+      <c r="P79" s="6"/>
+      <c r="Q79" s="6"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="6"/>
+      <c r="T79" s="6"/>
+      <c r="U79" s="6"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N80" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="O80" s="6"/>
-      <c r="P80" s="6"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
-    </row>
-    <row r="81" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N81" s="6" t="s">
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="5"/>
+      <c r="R80" s="5"/>
+      <c r="S80" s="5"/>
+      <c r="T80" s="5"/>
+      <c r="U80" s="5"/>
+    </row>
+    <row r="81" spans="14:21" x14ac:dyDescent="0.25">
+      <c r="N81" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="O81" s="6"/>
-      <c r="P81" s="6"/>
-      <c r="Q81" s="6"/>
-      <c r="R81" s="6"/>
-      <c r="S81" s="6"/>
-      <c r="T81" s="6"/>
-      <c r="U81" s="6"/>
-    </row>
-    <row r="82" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N82" s="6" t="s">
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="5"/>
+      <c r="R81" s="5"/>
+      <c r="S81" s="5"/>
+      <c r="T81" s="5"/>
+      <c r="U81" s="5"/>
+    </row>
+    <row r="82" spans="14:21" x14ac:dyDescent="0.25">
+      <c r="N82" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="O82" s="6"/>
-      <c r="P82" s="6"/>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="5"/>
+      <c r="R82" s="5"/>
+      <c r="S82" s="5"/>
+      <c r="T82" s="5"/>
+      <c r="U82" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="F45:L45"/>
-    <mergeCell ref="F46:L46"/>
-    <mergeCell ref="F39:L39"/>
-    <mergeCell ref="F41:L41"/>
-    <mergeCell ref="F42:L42"/>
-    <mergeCell ref="F44:L44"/>
-    <mergeCell ref="F43:L43"/>
-    <mergeCell ref="F35:L35"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="F37:L37"/>
-    <mergeCell ref="F38:L38"/>
-    <mergeCell ref="F30:L30"/>
-    <mergeCell ref="F31:L31"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="F33:L33"/>
-    <mergeCell ref="F34:L34"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="F26:L26"/>
-    <mergeCell ref="F27:L27"/>
-    <mergeCell ref="H28:L28"/>
-    <mergeCell ref="F29:L29"/>
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="F21:L21"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="F23:L23"/>
-    <mergeCell ref="F24:L24"/>
-    <mergeCell ref="F15:L15"/>
-    <mergeCell ref="F16:L16"/>
-    <mergeCell ref="F17:L17"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="F19:L19"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A63:D63"/>
     <mergeCell ref="A2:D2"/>
@@ -9124,6 +9082,39 @@
     <mergeCell ref="F12:L12"/>
     <mergeCell ref="G14:L14"/>
     <mergeCell ref="F13:L13"/>
+    <mergeCell ref="F15:L15"/>
+    <mergeCell ref="F16:L16"/>
+    <mergeCell ref="F17:L17"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="F19:L19"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="F21:L21"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="F23:L23"/>
+    <mergeCell ref="F24:L24"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="F26:L26"/>
+    <mergeCell ref="F27:L27"/>
+    <mergeCell ref="H28:L28"/>
+    <mergeCell ref="F29:L29"/>
+    <mergeCell ref="F35:L35"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="F37:L37"/>
+    <mergeCell ref="F38:L38"/>
+    <mergeCell ref="F30:L30"/>
+    <mergeCell ref="F31:L31"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="F34:L34"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="F45:L45"/>
+    <mergeCell ref="F46:L46"/>
+    <mergeCell ref="F39:L39"/>
+    <mergeCell ref="F41:L41"/>
+    <mergeCell ref="F42:L42"/>
+    <mergeCell ref="F44:L44"/>
+    <mergeCell ref="F43:L43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
